--- a/Stay URLs_tnm_flagged.xlsx
+++ b/Stay URLs_tnm_flagged.xlsx
@@ -524,7 +524,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>xrf, rvi, ndt, NDT</t>
+          <t>xrf, rvi, NDT</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>XRF / XRD Analyzers; Remote Visual Inspection (RVI); Ultrasonic Testing (UT); Non-Destructive Testing (NDT/NDE)</t>
+          <t>XRF / XRD Analyzers; Remote Visual Inspection (RVI); Ultrasonic Testing (UT)</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>xrf, Vanta, rvi, ultrasonic flaw, OmniScan, nde</t>
+          <t>xrf, Vanta, rvi, ultrasonic flaw, OmniScan</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1049,29 +1049,17 @@
       <c r="E15" t="n">
         <v>5951</v>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Remote Visual Inspection (RVI); Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>rvi, inspection system</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -1182,26 +1170,14 @@
       <c r="E18" t="n">
         <v>1843</v>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>Live</t>
@@ -1239,17 +1215,17 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Remote Visual Inspection (RVI); Non-Destructive Testing (NDT/NDE)</t>
+          <t>Remote Visual Inspection (RVI)</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>rvi, nde</t>
+          <t>rvi</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1284,17 +1260,17 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Remote Visual Inspection (RVI); Non-Destructive Testing (NDT/NDE)</t>
+          <t>Remote Visual Inspection (RVI)</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>rvi, nde</t>
+          <t>rvi</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1405,26 +1381,14 @@
       <c r="E23" t="n">
         <v>928</v>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>Live</t>
@@ -1488,26 +1452,14 @@
       <c r="E25" t="n">
         <v>1133</v>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>Live</t>
@@ -1545,17 +1497,17 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Remote Visual Inspection (RVI); Non-Destructive Testing (NDT/NDE)</t>
+          <t>Remote Visual Inspection (RVI)</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>rvi, inspection system</t>
+          <t>rvi</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1588,29 +1540,17 @@
       <c r="E27" t="n">
         <v>4402</v>
       </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -1633,26 +1573,14 @@
       <c r="E28" t="n">
         <v>5533</v>
       </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>Live</t>
@@ -1837,17 +1765,17 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Remote Visual Inspection (RVI); Non-Destructive Testing (NDT/NDE)</t>
+          <t>Remote Visual Inspection (RVI)</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>rvi, nde</t>
+          <t>rvi</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2221,17 +2149,17 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Non-Destructive Testing (NDT/NDE); Industrial Videoscopes / Inspection Tools</t>
+          <t>Industrial Videoscopes / Inspection Tools</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>nde, 3d measurement</t>
+          <t>3d measurement</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2264,26 +2192,14 @@
       <c r="E44" t="n">
         <v>3920</v>
       </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
           <t>Live</t>
@@ -2309,26 +2225,14 @@
       <c r="E45" t="n">
         <v>1828</v>
       </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
           <t>Live</t>
@@ -2407,7 +2311,7 @@
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -2468,26 +2372,14 @@
       <c r="E49" t="n">
         <v>5873</v>
       </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
           <t>Live</t>
@@ -2513,26 +2405,14 @@
       <c r="E50" t="n">
         <v>4696</v>
       </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
           <t>Live</t>
@@ -2591,26 +2471,14 @@
       <c r="E52" t="n">
         <v>4619</v>
       </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
           <t>Live</t>
@@ -2641,29 +2509,17 @@
       <c r="E53" t="n">
         <v>4631</v>
       </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -2686,26 +2542,14 @@
       <c r="E54" t="n">
         <v>3665</v>
       </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>inspection system</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
           <t>Live</t>
@@ -2743,12 +2587,12 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Remote Visual Inspection (RVI); Ultrasonic Testing (UT); Non-Destructive Testing (NDT/NDE)</t>
+          <t>Remote Visual Inspection (RVI); Ultrasonic Testing (UT)</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>rvi, EPOCH, Epoch, nde</t>
+          <t>rvi, EPOCH, Epoch</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2900,26 +2744,14 @@
       <c r="E59" t="n">
         <v>4552</v>
       </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
           <t>Live</t>
@@ -3102,26 +2934,14 @@
       <c r="E64" t="n">
         <v>4736</v>
       </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>inspection system</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
           <t>Live</t>
@@ -3375,26 +3195,14 @@
       <c r="E71" t="n">
         <v>2030</v>
       </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>inspection system</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
           <t>Live</t>
@@ -3558,26 +3366,14 @@
       <c r="E75" t="n">
         <v>183</v>
       </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
           <t>Live</t>
@@ -3608,26 +3404,14 @@
       <c r="E76" t="n">
         <v>3425</v>
       </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
           <t>Live</t>
@@ -3668,7 +3452,7 @@
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -3753,17 +3537,17 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Non-Destructive Testing (NDT/NDE); Industrial Videoscopes / Inspection Tools</t>
+          <t>Industrial Videoscopes / Inspection Tools</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>nde, 3d measurement</t>
+          <t>3d measurement</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -3879,17 +3663,17 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Non-Destructive Testing (NDT/NDE); Industrial Videoscopes / Inspection Tools</t>
+          <t>Industrial Videoscopes / Inspection Tools</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>nde, 3d measurement</t>
+          <t>3d measurement</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -3979,17 +3763,17 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Remote Visual Inspection (RVI); Non-Destructive Testing (NDT/NDE)</t>
+          <t>Remote Visual Inspection (RVI)</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>rvi, nde</t>
+          <t>rvi</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -4032,7 +3816,7 @@
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -4105,7 +3889,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>rvi, phased array, nondestructive testing, nde</t>
+          <t>rvi, phased array, nondestructive testing</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -4143,29 +3927,17 @@
       <c r="E88" t="n">
         <v>288</v>
       </c>
-      <c r="F88" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -4195,12 +3967,12 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Remote Visual Inspection (RVI); Non-Destructive Testing (NDT/NDE); Industrial Videoscopes / Inspection Tools</t>
+          <t>Remote Visual Inspection (RVI); Industrial Videoscopes / Inspection Tools</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>remote visual inspection, videoscope, borescope, IPLEX, nde, iplex, IPLEX G</t>
+          <t>remote visual inspection, videoscope, borescope, IPLEX, iplex, IPLEX G</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -4238,29 +4010,17 @@
       <c r="E90" t="n">
         <v>4124</v>
       </c>
-      <c r="F90" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -4283,26 +4043,14 @@
       <c r="E91" t="n">
         <v>3177</v>
       </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F91" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr">
         <is>
           <t>Live</t>
@@ -4333,26 +4081,14 @@
       <c r="E92" t="n">
         <v>998</v>
       </c>
-      <c r="F92" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F92" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr">
         <is>
           <t>Live</t>
@@ -4383,26 +4119,14 @@
       <c r="E93" t="n">
         <v>5519</v>
       </c>
-      <c r="F93" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F93" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr">
         <is>
           <t>Live</t>
@@ -4471,29 +4195,17 @@
       <c r="E95" t="n">
         <v>4790</v>
       </c>
-      <c r="F95" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>Remote Visual Inspection (RVI); Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>rvi, nde</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="F95" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -4531,7 +4243,7 @@
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -4554,26 +4266,14 @@
       <c r="E97" t="n">
         <v>3755</v>
       </c>
-      <c r="F97" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F97" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr">
         <is>
           <t>Live</t>
@@ -4718,26 +4418,14 @@
       <c r="E101" t="n">
         <v>3594</v>
       </c>
-      <c r="F101" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F101" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr">
         <is>
           <t>Live</t>
@@ -4778,7 +4466,7 @@
       <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -4927,26 +4615,14 @@
       <c r="E106" t="n">
         <v>1981</v>
       </c>
-      <c r="F106" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F106" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr">
         <is>
           <t>Live</t>
@@ -5191,7 +4867,7 @@
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -5262,7 +4938,7 @@
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -5300,7 +4976,7 @@
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -5328,26 +5004,14 @@
       <c r="E116" t="n">
         <v>3893</v>
       </c>
-      <c r="F116" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F116" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr">
         <is>
           <t>Live</t>
@@ -5613,17 +5277,17 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Non-Destructive Testing (NDT/NDE); Industrial Videoscopes / Inspection Tools</t>
+          <t>Industrial Videoscopes / Inspection Tools</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>nde, 3d measurement</t>
+          <t>3d measurement</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -5984,7 +5648,7 @@
       <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -6050,26 +5714,14 @@
       <c r="E134" t="n">
         <v>4653</v>
       </c>
-      <c r="F134" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F134" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr"/>
+      <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr">
         <is>
           <t>Live</t>
@@ -6110,7 +5762,7 @@
       <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -6171,26 +5823,14 @@
       <c r="E137" t="n">
         <v>2367</v>
       </c>
-      <c r="F137" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F137" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr"/>
+      <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr">
         <is>
           <t>Live</t>
@@ -6223,17 +5863,17 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Non-Destructive Testing (NDT/NDE); Industrial Videoscopes / Inspection Tools</t>
+          <t>Industrial Videoscopes / Inspection Tools</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>nde, 3d measurement</t>
+          <t>3d measurement</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -6261,26 +5901,14 @@
       <c r="E139" t="n">
         <v>2586</v>
       </c>
-      <c r="F139" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F139" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr"/>
+      <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr">
         <is>
           <t>Live</t>
@@ -6412,17 +6040,17 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Non-Destructive Testing (NDT/NDE); Industrial Videoscopes / Inspection Tools</t>
+          <t>Industrial Videoscopes / Inspection Tools</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>nde, 3d measurement</t>
+          <t>3d measurement</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -6890,17 +6518,17 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>XRF / XRD Analyzers; Non-Destructive Testing (NDT/NDE)</t>
+          <t>XRF / XRD Analyzers</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>xrf, x-ray fluorescence, nde</t>
+          <t>xrf, x-ray fluorescence</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -7021,26 +6649,14 @@
       <c r="E159" t="n">
         <v>3358</v>
       </c>
-      <c r="F159" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F159" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr"/>
       <c r="J159" t="inlineStr">
         <is>
           <t>Live</t>
@@ -7071,29 +6687,17 @@
       <c r="E160" t="n">
         <v>2392</v>
       </c>
-      <c r="F160" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F160" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr"/>
+      <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr"/>
       <c r="J160" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -7116,26 +6720,14 @@
       <c r="E161" t="n">
         <v>2396</v>
       </c>
-      <c r="F161" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F161" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr"/>
+      <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr"/>
       <c r="J161" t="inlineStr">
         <is>
           <t>Live</t>
@@ -7386,17 +6978,17 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Remote Visual Inspection (RVI); Non-Destructive Testing (NDT/NDE)</t>
+          <t>Remote Visual Inspection (RVI)</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>rvi, nde</t>
+          <t>rvi</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -7431,17 +7023,17 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Remote Visual Inspection (RVI); Non-Destructive Testing (NDT/NDE)</t>
+          <t>Remote Visual Inspection (RVI)</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>rvi, nde</t>
+          <t>rvi</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -7474,29 +7066,17 @@
       <c r="E170" t="n">
         <v>2977</v>
       </c>
-      <c r="F170" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F170" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr"/>
+      <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr"/>
       <c r="J170" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -7519,26 +7099,14 @@
       <c r="E171" t="n">
         <v>662</v>
       </c>
-      <c r="F171" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F171" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr"/>
+      <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr"/>
       <c r="J171" t="inlineStr">
         <is>
           <t>Live</t>
@@ -7730,17 +7298,17 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Ultrasonic Testing (UT); Non-Destructive Testing (NDT/NDE)</t>
+          <t>Ultrasonic Testing (UT)</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>thickness measurement, nde</t>
+          <t>thickness measurement</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -7768,26 +7336,14 @@
       <c r="E177" t="n">
         <v>2390</v>
       </c>
-      <c r="F177" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F177" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr"/>
+      <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr"/>
       <c r="J177" t="inlineStr">
         <is>
           <t>Live</t>
@@ -7965,26 +7521,14 @@
       <c r="E182" t="n">
         <v>5139</v>
       </c>
-      <c r="F182" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>nde, inspection system</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="F182" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr"/>
+      <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr"/>
       <c r="J182" t="inlineStr">
         <is>
           <t>Live</t>
@@ -8010,26 +7554,14 @@
       <c r="E183" t="n">
         <v>4824</v>
       </c>
-      <c r="F183" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>nde, inspection system</t>
-        </is>
-      </c>
-      <c r="I183" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="F183" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr"/>
+      <c r="H183" t="inlineStr"/>
+      <c r="I183" t="inlineStr"/>
       <c r="J183" t="inlineStr">
         <is>
           <t>Live</t>
@@ -8093,26 +7625,14 @@
       <c r="E185" t="n">
         <v>1000</v>
       </c>
-      <c r="F185" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F185" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr"/>
+      <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr"/>
       <c r="J185" t="inlineStr">
         <is>
           <t>Live</t>
@@ -8176,26 +7696,14 @@
       <c r="E187" t="n">
         <v>3633</v>
       </c>
-      <c r="F187" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I187" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F187" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr"/>
+      <c r="I187" t="inlineStr"/>
       <c r="J187" t="inlineStr">
         <is>
           <t>Live</t>
@@ -8226,29 +7734,17 @@
       <c r="E188" t="n">
         <v>3977</v>
       </c>
-      <c r="F188" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>Remote Visual Inspection (RVI); Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>rvi, nde</t>
-        </is>
-      </c>
-      <c r="I188" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="F188" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr"/>
+      <c r="I188" t="inlineStr"/>
       <c r="J188" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -8444,12 +7940,12 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Remote Visual Inspection (RVI); Ultrasonic Testing (UT); Non-Destructive Testing (NDT/NDE)</t>
+          <t>Remote Visual Inspection (RVI); Ultrasonic Testing (UT)</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>rvi, phased array, OmniScan, nde</t>
+          <t>rvi, phased array, OmniScan</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -8482,26 +7978,14 @@
       <c r="E194" t="n">
         <v>5785</v>
       </c>
-      <c r="F194" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I194" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F194" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr"/>
+      <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr"/>
       <c r="J194" t="inlineStr">
         <is>
           <t>Live</t>
@@ -8788,26 +8272,14 @@
       <c r="E202" t="n">
         <v>2975</v>
       </c>
-      <c r="F202" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>nde, inspection system</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="F202" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr"/>
+      <c r="H202" t="inlineStr"/>
+      <c r="I202" t="inlineStr"/>
       <c r="J202" t="inlineStr">
         <is>
           <t>Live</t>
@@ -8997,17 +8469,17 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Remote Visual Inspection (RVI); Non-Destructive Testing (NDT/NDE)</t>
+          <t>Remote Visual Inspection (RVI)</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>rvi, nde</t>
+          <t>rvi</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
@@ -9676,26 +9148,14 @@
       <c r="E225" t="n">
         <v>5055</v>
       </c>
-      <c r="F225" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G225" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H225" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I225" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F225" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr"/>
+      <c r="H225" t="inlineStr"/>
+      <c r="I225" t="inlineStr"/>
       <c r="J225" t="inlineStr">
         <is>
           <t>Live</t>
@@ -9726,26 +9186,14 @@
       <c r="E226" t="n">
         <v>5059</v>
       </c>
-      <c r="F226" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G226" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H226" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I226" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F226" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr"/>
+      <c r="H226" t="inlineStr"/>
+      <c r="I226" t="inlineStr"/>
       <c r="J226" t="inlineStr">
         <is>
           <t>Live</t>
@@ -9928,26 +9376,14 @@
       <c r="E231" t="n">
         <v>4423</v>
       </c>
-      <c r="F231" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G231" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H231" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I231" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F231" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr"/>
+      <c r="H231" t="inlineStr"/>
+      <c r="I231" t="inlineStr"/>
       <c r="J231" t="inlineStr">
         <is>
           <t>Live</t>
@@ -9978,26 +9414,14 @@
       <c r="E232" t="n">
         <v>4422</v>
       </c>
-      <c r="F232" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G232" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H232" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I232" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F232" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr"/>
+      <c r="H232" t="inlineStr"/>
+      <c r="I232" t="inlineStr"/>
       <c r="J232" t="inlineStr">
         <is>
           <t>Live</t>
@@ -10066,26 +9490,14 @@
       <c r="E234" t="n">
         <v>4209</v>
       </c>
-      <c r="F234" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G234" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H234" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I234" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F234" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr"/>
+      <c r="H234" t="inlineStr"/>
+      <c r="I234" t="inlineStr"/>
       <c r="J234" t="inlineStr">
         <is>
           <t>Live</t>
@@ -10116,26 +9528,14 @@
       <c r="E235" t="n">
         <v>4208</v>
       </c>
-      <c r="F235" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G235" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H235" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I235" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F235" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr"/>
+      <c r="H235" t="inlineStr"/>
+      <c r="I235" t="inlineStr"/>
       <c r="J235" t="inlineStr">
         <is>
           <t>Live</t>
@@ -10546,26 +9946,14 @@
       <c r="E246" t="n">
         <v>3544</v>
       </c>
-      <c r="F246" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G246" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H246" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I246" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F246" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr"/>
+      <c r="H246" t="inlineStr"/>
+      <c r="I246" t="inlineStr"/>
       <c r="J246" t="inlineStr">
         <is>
           <t>Live</t>
@@ -10596,26 +9984,14 @@
       <c r="E247" t="n">
         <v>3542</v>
       </c>
-      <c r="F247" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G247" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H247" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I247" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F247" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr"/>
+      <c r="H247" t="inlineStr"/>
+      <c r="I247" t="inlineStr"/>
       <c r="J247" t="inlineStr">
         <is>
           <t>Live</t>
@@ -10760,26 +10136,14 @@
       <c r="E251" t="n">
         <v>3513</v>
       </c>
-      <c r="F251" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G251" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H251" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I251" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F251" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr"/>
+      <c r="H251" t="inlineStr"/>
+      <c r="I251" t="inlineStr"/>
       <c r="J251" t="inlineStr">
         <is>
           <t>Live</t>
@@ -10810,26 +10174,14 @@
       <c r="E252" t="n">
         <v>638</v>
       </c>
-      <c r="F252" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G252" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H252" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I252" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F252" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr"/>
+      <c r="H252" t="inlineStr"/>
+      <c r="I252" t="inlineStr"/>
       <c r="J252" t="inlineStr">
         <is>
           <t>Live</t>
@@ -11012,26 +10364,14 @@
       <c r="E257" t="n">
         <v>2404</v>
       </c>
-      <c r="F257" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G257" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H257" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I257" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F257" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr"/>
+      <c r="H257" t="inlineStr"/>
+      <c r="I257" t="inlineStr"/>
       <c r="J257" t="inlineStr">
         <is>
           <t>Live</t>
@@ -11062,26 +10402,14 @@
       <c r="E258" t="n">
         <v>2402</v>
       </c>
-      <c r="F258" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G258" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H258" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I258" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F258" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr"/>
+      <c r="H258" t="inlineStr"/>
+      <c r="I258" t="inlineStr"/>
       <c r="J258" t="inlineStr">
         <is>
           <t>Live</t>
@@ -11264,26 +10592,14 @@
       <c r="E263" t="n">
         <v>2217</v>
       </c>
-      <c r="F263" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G263" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H263" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I263" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F263" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr"/>
+      <c r="H263" t="inlineStr"/>
+      <c r="I263" t="inlineStr"/>
       <c r="J263" t="inlineStr">
         <is>
           <t>Live</t>
@@ -11314,26 +10630,14 @@
       <c r="E264" t="n">
         <v>2202</v>
       </c>
-      <c r="F264" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G264" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H264" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I264" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F264" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr"/>
+      <c r="H264" t="inlineStr"/>
+      <c r="I264" t="inlineStr"/>
       <c r="J264" t="inlineStr">
         <is>
           <t>Live</t>
@@ -11478,26 +10782,14 @@
       <c r="E268" t="n">
         <v>3188</v>
       </c>
-      <c r="F268" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G268" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H268" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I268" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F268" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr"/>
+      <c r="H268" t="inlineStr"/>
+      <c r="I268" t="inlineStr"/>
       <c r="J268" t="inlineStr">
         <is>
           <t>Live</t>
@@ -11528,26 +10820,14 @@
       <c r="E269" t="n">
         <v>3190</v>
       </c>
-      <c r="F269" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G269" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H269" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I269" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F269" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr"/>
+      <c r="H269" t="inlineStr"/>
+      <c r="I269" t="inlineStr"/>
       <c r="J269" t="inlineStr">
         <is>
           <t>Live</t>
@@ -11692,26 +10972,14 @@
       <c r="E273" t="n">
         <v>2765</v>
       </c>
-      <c r="F273" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G273" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H273" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I273" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F273" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr"/>
+      <c r="H273" t="inlineStr"/>
+      <c r="I273" t="inlineStr"/>
       <c r="J273" t="inlineStr">
         <is>
           <t>Live</t>
@@ -11932,26 +11200,14 @@
       <c r="E279" t="n">
         <v>4095</v>
       </c>
-      <c r="F279" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G279" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H279" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I279" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F279" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr"/>
+      <c r="H279" t="inlineStr"/>
+      <c r="I279" t="inlineStr"/>
       <c r="J279" t="inlineStr">
         <is>
           <t>Live</t>
@@ -12210,26 +11466,14 @@
       <c r="E286" t="n">
         <v>3842</v>
       </c>
-      <c r="F286" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G286" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H286" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I286" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F286" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr"/>
+      <c r="H286" t="inlineStr"/>
+      <c r="I286" t="inlineStr"/>
       <c r="J286" t="inlineStr">
         <is>
           <t>Live</t>
@@ -12602,26 +11846,14 @@
       <c r="E296" t="n">
         <v>936</v>
       </c>
-      <c r="F296" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G296" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H296" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I296" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F296" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr"/>
+      <c r="H296" t="inlineStr"/>
+      <c r="I296" t="inlineStr"/>
       <c r="J296" t="inlineStr">
         <is>
           <t>Live</t>
@@ -12662,7 +11894,7 @@
       <c r="I297" t="inlineStr"/>
       <c r="J297" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -13004,7 +12236,7 @@
       <c r="I306" t="inlineStr"/>
       <c r="J306" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -14210,26 +13442,14 @@
       <c r="E338" t="n">
         <v>2295</v>
       </c>
-      <c r="F338" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G338" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H338" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I338" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F338" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr"/>
+      <c r="H338" t="inlineStr"/>
+      <c r="I338" t="inlineStr"/>
       <c r="J338" t="inlineStr">
         <is>
           <t>Live</t>
@@ -14830,26 +14050,14 @@
       <c r="E354" t="n">
         <v>3251</v>
       </c>
-      <c r="F354" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G354" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H354" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I354" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F354" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr"/>
+      <c r="H354" t="inlineStr"/>
+      <c r="I354" t="inlineStr"/>
       <c r="J354" t="inlineStr">
         <is>
           <t>Live</t>
@@ -15118,7 +14326,7 @@
       <c r="I361" t="inlineStr"/>
       <c r="J361" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -15156,7 +14364,7 @@
       <c r="I362" t="inlineStr"/>
       <c r="J362" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -15194,7 +14402,7 @@
       <c r="I363" t="inlineStr"/>
       <c r="J363" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -15232,7 +14440,7 @@
       <c r="I364" t="inlineStr"/>
       <c r="J364" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -16020,26 +15228,14 @@
       <c r="E385" t="n">
         <v>1736</v>
       </c>
-      <c r="F385" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G385" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H385" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I385" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F385" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr"/>
+      <c r="H385" t="inlineStr"/>
+      <c r="I385" t="inlineStr"/>
       <c r="J385" t="inlineStr">
         <is>
           <t>Live</t>
@@ -16080,7 +15276,7 @@
       <c r="I386" t="inlineStr"/>
       <c r="J386" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -16146,26 +15342,14 @@
       <c r="E388" t="n">
         <v>1785</v>
       </c>
-      <c r="F388" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G388" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H388" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I388" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F388" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr"/>
+      <c r="H388" t="inlineStr"/>
+      <c r="I388" t="inlineStr"/>
       <c r="J388" t="inlineStr">
         <is>
           <t>Live</t>
@@ -16196,26 +15380,14 @@
       <c r="E389" t="n">
         <v>1800</v>
       </c>
-      <c r="F389" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G389" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H389" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I389" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F389" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr"/>
+      <c r="H389" t="inlineStr"/>
+      <c r="I389" t="inlineStr"/>
       <c r="J389" t="inlineStr">
         <is>
           <t>Live</t>
@@ -16322,26 +15494,14 @@
       <c r="E392" t="n">
         <v>1658</v>
       </c>
-      <c r="F392" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G392" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H392" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I392" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F392" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr"/>
+      <c r="H392" t="inlineStr"/>
+      <c r="I392" t="inlineStr"/>
       <c r="J392" t="inlineStr">
         <is>
           <t>Live</t>
@@ -16372,26 +15532,14 @@
       <c r="E393" t="n">
         <v>1803</v>
       </c>
-      <c r="F393" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G393" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H393" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I393" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F393" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr"/>
+      <c r="H393" t="inlineStr"/>
+      <c r="I393" t="inlineStr"/>
       <c r="J393" t="inlineStr">
         <is>
           <t>Live</t>
@@ -16574,26 +15722,14 @@
       <c r="E398" t="n">
         <v>1745</v>
       </c>
-      <c r="F398" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G398" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H398" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I398" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F398" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr"/>
+      <c r="H398" t="inlineStr"/>
+      <c r="I398" t="inlineStr"/>
       <c r="J398" t="inlineStr">
         <is>
           <t>Live</t>
@@ -16748,7 +15884,7 @@
       <c r="I402" t="inlineStr"/>
       <c r="J402" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -16776,26 +15912,14 @@
       <c r="E403" t="n">
         <v>1796</v>
       </c>
-      <c r="F403" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G403" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H403" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I403" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F403" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr"/>
+      <c r="H403" t="inlineStr"/>
+      <c r="I403" t="inlineStr"/>
       <c r="J403" t="inlineStr">
         <is>
           <t>Live</t>
@@ -16940,26 +16064,14 @@
       <c r="E407" t="n">
         <v>1739</v>
       </c>
-      <c r="F407" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G407" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H407" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I407" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F407" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr"/>
+      <c r="H407" t="inlineStr"/>
+      <c r="I407" t="inlineStr"/>
       <c r="J407" t="inlineStr">
         <is>
           <t>Live</t>
@@ -17180,26 +16292,14 @@
       <c r="E413" t="n">
         <v>1787</v>
       </c>
-      <c r="F413" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G413" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H413" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I413" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F413" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr"/>
+      <c r="H413" t="inlineStr"/>
+      <c r="I413" t="inlineStr"/>
       <c r="J413" t="inlineStr">
         <is>
           <t>Live</t>
@@ -17572,26 +16672,14 @@
       <c r="E423" t="n">
         <v>1681</v>
       </c>
-      <c r="F423" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G423" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H423" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I423" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F423" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr"/>
+      <c r="H423" t="inlineStr"/>
+      <c r="I423" t="inlineStr"/>
       <c r="J423" t="inlineStr">
         <is>
           <t>Live</t>
@@ -17708,7 +16796,7 @@
       <c r="I426" t="inlineStr"/>
       <c r="J426" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -17784,7 +16872,7 @@
       <c r="I428" t="inlineStr"/>
       <c r="J428" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -17974,7 +17062,7 @@
       <c r="I433" t="inlineStr"/>
       <c r="J433" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -18012,7 +17100,7 @@
       <c r="I434" t="inlineStr"/>
       <c r="J434" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -18088,7 +17176,7 @@
       <c r="I436" t="inlineStr"/>
       <c r="J436" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -18572,7 +17660,7 @@
       <c r="I449" t="inlineStr"/>
       <c r="J449" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -18688,7 +17776,7 @@
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>xrf, x-ray fluorescence, handheld xrf, Vanta, remote visual inspection, rvi, phased array, tofd, time-of-flight diffraction, OmniScan, nondestructive testing, ndt, nde, NDT</t>
+          <t>xrf, x-ray fluorescence, handheld xrf, Vanta, remote visual inspection, rvi, phased array, tofd, time-of-flight diffraction, OmniScan, nondestructive testing, NDT</t>
         </is>
       </c>
       <c r="I452" t="inlineStr">
@@ -18809,7 +17897,7 @@
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t>xrf, x-ray fluorescence, portable xrf, pxrf, Vanta, remote visual inspection, rvi, videoscope, borescope, IPLEX, ultrasonic testing, ultrasonic inspection, phased array, paut, weld inspection, OmniScan, Omniscan, nondestructive testing, ndt, nde, eddy current, NDT, iplex, IPLEX One</t>
+          <t>xrf, x-ray fluorescence, portable xrf, pxrf, Vanta, remote visual inspection, rvi, videoscope, borescope, IPLEX, ultrasonic testing, ultrasonic inspection, phased array, paut, weld inspection, OmniScan, Omniscan, nondestructive testing, eddy current, NDT, iplex, IPLEX One</t>
         </is>
       </c>
       <c r="I455" t="inlineStr">
@@ -18920,7 +18008,7 @@
       </c>
       <c r="H458" t="inlineStr">
         <is>
-          <t>rvi, ndt, NDT</t>
+          <t>rvi, NDT</t>
         </is>
       </c>
       <c r="I458" t="inlineStr">
@@ -19304,7 +18392,7 @@
       </c>
       <c r="H468" t="inlineStr">
         <is>
-          <t>xrf, videoscope, IPLEX, phased array, paut, OmniScan, ndt, nde, NDT, iplex</t>
+          <t>xrf, videoscope, IPLEX, phased array, paut, OmniScan, NDT, iplex</t>
         </is>
       </c>
       <c r="I468" t="inlineStr">
@@ -20258,26 +19346,14 @@
       <c r="E496" t="n">
         <v>241</v>
       </c>
-      <c r="F496" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G496" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H496" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I496" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F496" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G496" t="inlineStr"/>
+      <c r="H496" t="inlineStr"/>
+      <c r="I496" t="inlineStr"/>
       <c r="J496" t="inlineStr">
         <is>
           <t>Live</t>
@@ -20429,7 +19505,7 @@
       </c>
       <c r="H500" t="inlineStr">
         <is>
-          <t>xrf, videoscope, IPLEX, phased array, paut, OmniScan, ndt, nde, NDT, iplex</t>
+          <t>xrf, videoscope, IPLEX, phased array, paut, OmniScan, NDT, iplex</t>
         </is>
       </c>
       <c r="I500" t="inlineStr">
@@ -20474,7 +19550,7 @@
       </c>
       <c r="H501" t="inlineStr">
         <is>
-          <t>xrf, ndt, NDT</t>
+          <t>xrf, NDT</t>
         </is>
       </c>
       <c r="I501" t="inlineStr">
@@ -20519,7 +19595,7 @@
       </c>
       <c r="H502" t="inlineStr">
         <is>
-          <t>xrf, handheld xrf, rvi, videoscope, ndt, NDT</t>
+          <t>xrf, handheld xrf, rvi, videoscope, NDT</t>
         </is>
       </c>
       <c r="I502" t="inlineStr">
@@ -20609,7 +19685,7 @@
       </c>
       <c r="H504" t="inlineStr">
         <is>
-          <t>xrf, xrd, portable xrf, phased array, ndt, eddy current, NDT</t>
+          <t>xrf, xrd, portable xrf, phased array, eddy current, NDT</t>
         </is>
       </c>
       <c r="I504" t="inlineStr">
@@ -20744,7 +19820,7 @@
       </c>
       <c r="H507" t="inlineStr">
         <is>
-          <t>xrf, xrd, handheld xrf, portable xrf, Vanta, phased array, OmniScan, ndt, NDT</t>
+          <t>xrf, xrd, handheld xrf, portable xrf, Vanta, phased array, OmniScan, NDT</t>
         </is>
       </c>
       <c r="I507" t="inlineStr">
@@ -20789,7 +19865,7 @@
       </c>
       <c r="H508" t="inlineStr">
         <is>
-          <t>xrf, xrd, pxrf, videoscope, phased array, OmniScan, ndt, nde, eddy current, NDT, NDE</t>
+          <t>xrf, xrd, pxrf, videoscope, phased array, OmniScan, eddy current, NDT, NDE</t>
         </is>
       </c>
       <c r="I508" t="inlineStr">
@@ -20879,7 +19955,7 @@
       </c>
       <c r="H510" t="inlineStr">
         <is>
-          <t>xrf, portable xrf, rvi, videoscope, turbine inspection, phased array, ndt, inspection system, NDT</t>
+          <t>xrf, portable xrf, rvi, videoscope, turbine inspection, phased array, NDT</t>
         </is>
       </c>
       <c r="I510" t="inlineStr">
@@ -20924,7 +20000,7 @@
       </c>
       <c r="H511" t="inlineStr">
         <is>
-          <t>rvi, videoscope, IPLEX, paut, OmniScan, ndt, NDT, iplex</t>
+          <t>rvi, videoscope, IPLEX, paut, OmniScan, NDT, iplex</t>
         </is>
       </c>
       <c r="I511" t="inlineStr">
@@ -21009,17 +20085,17 @@
       </c>
       <c r="G513" t="inlineStr">
         <is>
-          <t>XRF / XRD Analyzers; Non-Destructive Testing (NDT/NDE)</t>
+          <t>XRF / XRD Analyzers</t>
         </is>
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t>xrf, handheld xrf, nde</t>
+          <t>xrf, handheld xrf</t>
         </is>
       </c>
       <c r="I513" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J513" t="inlineStr">
@@ -21054,12 +20130,12 @@
       </c>
       <c r="G514" t="inlineStr">
         <is>
-          <t>XRF / XRD Analyzers; Remote Visual Inspection (RVI); Ultrasonic Testing (UT); Non-Destructive Testing (NDT/NDE)</t>
+          <t>XRF / XRD Analyzers; Remote Visual Inspection (RVI); Ultrasonic Testing (UT)</t>
         </is>
       </c>
       <c r="H514" t="inlineStr">
         <is>
-          <t>xrf, x-ray fluorescence, handheld xrf, Vanta, rvi, videoscope, weld inspection, OmniScan, nde</t>
+          <t>xrf, x-ray fluorescence, handheld xrf, Vanta, rvi, videoscope, weld inspection, OmniScan</t>
         </is>
       </c>
       <c r="I514" t="inlineStr">
@@ -21104,7 +20180,7 @@
       </c>
       <c r="H515" t="inlineStr">
         <is>
-          <t>xrf, handheld xrf, Vanta, videoscope, OmniScan, ndt, NDT</t>
+          <t>xrf, handheld xrf, Vanta, videoscope, OmniScan, NDT</t>
         </is>
       </c>
       <c r="I515" t="inlineStr">
@@ -21194,7 +20270,7 @@
       </c>
       <c r="H517" t="inlineStr">
         <is>
-          <t>xrf, ndt, NDT</t>
+          <t>xrf, NDT</t>
         </is>
       </c>
       <c r="I517" t="inlineStr">
@@ -21329,7 +20405,7 @@
       </c>
       <c r="H520" t="inlineStr">
         <is>
-          <t>xrf, handheld xrf, Vanta, rvi, ndt, NDT</t>
+          <t>xrf, handheld xrf, Vanta, rvi, NDT</t>
         </is>
       </c>
       <c r="I520" t="inlineStr">
@@ -21374,7 +20450,7 @@
       </c>
       <c r="H521" t="inlineStr">
         <is>
-          <t>xrf, xrd, handheld xrf, Vanta, ndt, NDT</t>
+          <t>xrf, xrd, handheld xrf, Vanta, NDT</t>
         </is>
       </c>
       <c r="I521" t="inlineStr">
@@ -21549,12 +20625,12 @@
       </c>
       <c r="G525" t="inlineStr">
         <is>
-          <t>XRF / XRD Analyzers; Remote Visual Inspection (RVI); Ultrasonic Testing (UT); Non-Destructive Testing (NDT/NDE)</t>
+          <t>XRF / XRD Analyzers; Remote Visual Inspection (RVI); Ultrasonic Testing (UT)</t>
         </is>
       </c>
       <c r="H525" t="inlineStr">
         <is>
-          <t>xrf, x-ray fluorescence, xrd, handheld xrf, Vanta, videoscope, borescope, phased array, inspection system</t>
+          <t>xrf, x-ray fluorescence, xrd, handheld xrf, Vanta, videoscope, borescope, phased array</t>
         </is>
       </c>
       <c r="I525" t="inlineStr">
@@ -21639,12 +20715,12 @@
       </c>
       <c r="G527" t="inlineStr">
         <is>
-          <t>XRF / XRD Analyzers; Non-Destructive Testing (NDT/NDE)</t>
+          <t>XRF / XRD Analyzers</t>
         </is>
       </c>
       <c r="H527" t="inlineStr">
         <is>
-          <t>xrf, handheld xrf, Vanta, nde</t>
+          <t>xrf, handheld xrf, Vanta</t>
         </is>
       </c>
       <c r="I527" t="inlineStr">
@@ -21689,7 +20765,7 @@
       </c>
       <c r="H528" t="inlineStr">
         <is>
-          <t>xrf, x-ray fluorescence, xrd, portable xrf, positive material identification, nondestructive testing, ndt, nde, NDT</t>
+          <t>xrf, x-ray fluorescence, xrd, portable xrf, positive material identification, nondestructive testing, NDT</t>
         </is>
       </c>
       <c r="I528" t="inlineStr">
@@ -21774,12 +20850,12 @@
       </c>
       <c r="G530" t="inlineStr">
         <is>
-          <t>XRF / XRD Analyzers; Non-Destructive Testing (NDT/NDE)</t>
+          <t>XRF / XRD Analyzers</t>
         </is>
       </c>
       <c r="H530" t="inlineStr">
         <is>
-          <t>xrf, x-ray fluorescence, handheld xrf, Vanta, nde</t>
+          <t>xrf, x-ray fluorescence, handheld xrf, Vanta</t>
         </is>
       </c>
       <c r="I530" t="inlineStr">
@@ -21959,7 +21035,7 @@
       </c>
       <c r="H534" t="inlineStr">
         <is>
-          <t>xrf, elemental analysis, Vanta, video borescope, borescope, turbine inspection, OmniScan, nde, NDE</t>
+          <t>xrf, elemental analysis, Vanta, video borescope, borescope, turbine inspection, OmniScan, NDE</t>
         </is>
       </c>
       <c r="I534" t="inlineStr">
@@ -22049,7 +21125,7 @@
       </c>
       <c r="H536" t="inlineStr">
         <is>
-          <t>xrf, pxrf, borescope, ultrasonic inspection, phased array, ndt, eddy current, NDT</t>
+          <t>xrf, pxrf, borescope, ultrasonic inspection, phased array, eddy current, NDT</t>
         </is>
       </c>
       <c r="I536" t="inlineStr">
@@ -22286,12 +21362,12 @@
       </c>
       <c r="G542" t="inlineStr">
         <is>
-          <t>Ultrasonic Testing (UT); Non-Destructive Testing (NDT/NDE)</t>
+          <t>Ultrasonic Testing (UT)</t>
         </is>
       </c>
       <c r="H542" t="inlineStr">
         <is>
-          <t>OmniScan, nde</t>
+          <t>OmniScan</t>
         </is>
       </c>
       <c r="I542" t="inlineStr">
@@ -22485,17 +21561,17 @@
       </c>
       <c r="G547" t="inlineStr">
         <is>
-          <t>Remote Visual Inspection (RVI); Non-Destructive Testing (NDT/NDE)</t>
+          <t>Remote Visual Inspection (RVI)</t>
         </is>
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t>rvi, nde</t>
+          <t>rvi</t>
         </is>
       </c>
       <c r="I547" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J547" t="inlineStr">
@@ -22642,26 +21718,14 @@
       <c r="E551" t="n">
         <v>1265</v>
       </c>
-      <c r="F551" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G551" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H551" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I551" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F551" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr"/>
+      <c r="H551" t="inlineStr"/>
+      <c r="I551" t="inlineStr"/>
       <c r="J551" t="inlineStr">
         <is>
           <t>Live</t>
@@ -22927,7 +21991,7 @@
       </c>
       <c r="H558" t="inlineStr">
         <is>
-          <t>rvi, ultrasonic testing, phased array, paut, nondestructive testing, ndt, nde, eddy current, liquid penetrant, NDT</t>
+          <t>rvi, ultrasonic testing, phased array, paut, nondestructive testing, eddy current, liquid penetrant, NDT</t>
         </is>
       </c>
       <c r="I558" t="inlineStr">
@@ -23169,17 +22233,17 @@
       </c>
       <c r="G564" t="inlineStr">
         <is>
-          <t>Remote Visual Inspection (RVI); Non-Destructive Testing (NDT/NDE)</t>
+          <t>Remote Visual Inspection (RVI)</t>
         </is>
       </c>
       <c r="H564" t="inlineStr">
         <is>
-          <t>rvi, nde, inspection system</t>
+          <t>rvi</t>
         </is>
       </c>
       <c r="I564" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J564" t="inlineStr">
@@ -23212,29 +22276,17 @@
       <c r="E565" t="n">
         <v>4046</v>
       </c>
-      <c r="F565" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G565" t="inlineStr">
-        <is>
-          <t>Remote Visual Inspection (RVI)</t>
-        </is>
-      </c>
-      <c r="H565" t="inlineStr">
-        <is>
-          <t>rvi</t>
-        </is>
-      </c>
-      <c r="I565" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F565" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr"/>
+      <c r="H565" t="inlineStr"/>
+      <c r="I565" t="inlineStr"/>
       <c r="J565" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -23290,26 +22342,14 @@
       <c r="E567" t="n">
         <v>1030</v>
       </c>
-      <c r="F567" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G567" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H567" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I567" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F567" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr"/>
+      <c r="H567" t="inlineStr"/>
+      <c r="I567" t="inlineStr"/>
       <c r="J567" t="inlineStr">
         <is>
           <t>Live</t>
@@ -23378,26 +22418,14 @@
       <c r="E569" t="n">
         <v>5664</v>
       </c>
-      <c r="F569" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G569" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H569" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I569" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F569" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr"/>
+      <c r="H569" t="inlineStr"/>
+      <c r="I569" t="inlineStr"/>
       <c r="J569" t="inlineStr">
         <is>
           <t>Live</t>
@@ -23478,7 +22506,7 @@
       </c>
       <c r="H571" t="inlineStr">
         <is>
-          <t>ndt, NDT</t>
+          <t>NDT</t>
         </is>
       </c>
       <c r="I571" t="inlineStr">
@@ -23523,7 +22551,7 @@
       </c>
       <c r="H572" t="inlineStr">
         <is>
-          <t>videoscope, borescope, ultrasonic testing, phased array, OmniScan, nondestructive testing, ndt, nde, eddy current, NDT</t>
+          <t>videoscope, borescope, ultrasonic testing, phased array, OmniScan, nondestructive testing, eddy current, NDT</t>
         </is>
       </c>
       <c r="I572" t="inlineStr">
@@ -23556,26 +22584,14 @@
       <c r="E573" t="n">
         <v>362</v>
       </c>
-      <c r="F573" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G573" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H573" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I573" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F573" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G573" t="inlineStr"/>
+      <c r="H573" t="inlineStr"/>
+      <c r="I573" t="inlineStr"/>
       <c r="J573" t="inlineStr">
         <is>
           <t>Live</t>
@@ -23613,7 +22629,7 @@
       </c>
       <c r="H574" t="inlineStr">
         <is>
-          <t>ndt, nde, NDT, NDE</t>
+          <t>NDT, NDE</t>
         </is>
       </c>
       <c r="I574" t="inlineStr">
@@ -23755,26 +22771,14 @@
       <c r="E578" t="n">
         <v>4896</v>
       </c>
-      <c r="F578" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G578" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H578" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I578" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F578" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G578" t="inlineStr"/>
+      <c r="H578" t="inlineStr"/>
+      <c r="I578" t="inlineStr"/>
       <c r="J578" t="inlineStr">
         <is>
           <t>Live</t>
@@ -23838,26 +22842,14 @@
       <c r="E580" t="n">
         <v>3377</v>
       </c>
-      <c r="F580" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G580" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H580" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I580" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F580" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G580" t="inlineStr"/>
+      <c r="H580" t="inlineStr"/>
+      <c r="I580" t="inlineStr"/>
       <c r="J580" t="inlineStr">
         <is>
           <t>Live</t>
@@ -23940,17 +22932,17 @@
       </c>
       <c r="G582" t="inlineStr">
         <is>
-          <t>XRF / XRD Analyzers; Non-Destructive Testing (NDT/NDE)</t>
+          <t>XRF / XRD Analyzers</t>
         </is>
       </c>
       <c r="H582" t="inlineStr">
         <is>
-          <t>xrf, nde</t>
+          <t>xrf</t>
         </is>
       </c>
       <c r="I582" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J582" t="inlineStr">
@@ -24220,26 +23212,14 @@
       <c r="E589" t="n">
         <v>4374</v>
       </c>
-      <c r="F589" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G589" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H589" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I589" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F589" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G589" t="inlineStr"/>
+      <c r="H589" t="inlineStr"/>
+      <c r="I589" t="inlineStr"/>
       <c r="J589" t="inlineStr">
         <is>
           <t>Live</t>
@@ -24545,17 +23525,17 @@
       </c>
       <c r="G597" t="inlineStr">
         <is>
-          <t>Remote Visual Inspection (RVI); Non-Destructive Testing (NDT/NDE)</t>
+          <t>Remote Visual Inspection (RVI)</t>
         </is>
       </c>
       <c r="H597" t="inlineStr">
         <is>
-          <t>rvi, nde</t>
+          <t>rvi</t>
         </is>
       </c>
       <c r="I597" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J597" t="inlineStr">
@@ -24633,7 +23613,7 @@
       </c>
       <c r="H599" t="inlineStr">
         <is>
-          <t>xrf, xrd, tofd, ndt, NDT</t>
+          <t>xrf, xrd, tofd, NDT</t>
         </is>
       </c>
       <c r="I599" t="inlineStr">
@@ -24666,26 +23646,14 @@
       <c r="E600" t="n">
         <v>1903</v>
       </c>
-      <c r="F600" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G600" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H600" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I600" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F600" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G600" t="inlineStr"/>
+      <c r="H600" t="inlineStr"/>
+      <c r="I600" t="inlineStr"/>
       <c r="J600" t="inlineStr">
         <is>
           <t>Live</t>
@@ -24718,12 +23686,12 @@
       </c>
       <c r="G601" t="inlineStr">
         <is>
-          <t>Remote Visual Inspection (RVI); Ultrasonic Testing (UT); Non-Destructive Testing (NDT/NDE)</t>
+          <t>Remote Visual Inspection (RVI); Ultrasonic Testing (UT)</t>
         </is>
       </c>
       <c r="H601" t="inlineStr">
         <is>
-          <t>pipeline inspection, ultrasonic testing, phased array, paut, tofd, time-of-flight diffraction, weld inspection, nde</t>
+          <t>pipeline inspection, ultrasonic testing, phased array, paut, tofd, time-of-flight diffraction, weld inspection</t>
         </is>
       </c>
       <c r="I601" t="inlineStr">
@@ -25074,17 +24042,17 @@
       </c>
       <c r="G610" t="inlineStr">
         <is>
-          <t>XRF / XRD Analyzers; Non-Destructive Testing (NDT/NDE)</t>
+          <t>XRF / XRD Analyzers</t>
         </is>
       </c>
       <c r="H610" t="inlineStr">
         <is>
-          <t>xrf, pxrf, nde</t>
+          <t>xrf, pxrf</t>
         </is>
       </c>
       <c r="I610" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J610" t="inlineStr">
@@ -25722,26 +24690,14 @@
       <c r="E627" t="n">
         <v>5397</v>
       </c>
-      <c r="F627" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G627" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H627" t="inlineStr">
-        <is>
-          <t>nde, inspection system</t>
-        </is>
-      </c>
-      <c r="I627" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="F627" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G627" t="inlineStr"/>
+      <c r="H627" t="inlineStr"/>
+      <c r="I627" t="inlineStr"/>
       <c r="J627" t="inlineStr">
         <is>
           <t>Live</t>
@@ -25772,26 +24728,14 @@
       <c r="E628" t="n">
         <v>2725</v>
       </c>
-      <c r="F628" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G628" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H628" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I628" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F628" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G628" t="inlineStr"/>
+      <c r="H628" t="inlineStr"/>
+      <c r="I628" t="inlineStr"/>
       <c r="J628" t="inlineStr">
         <is>
           <t>Live</t>
@@ -25855,26 +24799,14 @@
       <c r="E630" t="n">
         <v>1376</v>
       </c>
-      <c r="F630" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G630" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H630" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I630" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F630" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G630" t="inlineStr"/>
+      <c r="H630" t="inlineStr"/>
+      <c r="I630" t="inlineStr"/>
       <c r="J630" t="inlineStr">
         <is>
           <t>Live</t>
@@ -26092,7 +25024,7 @@
       </c>
       <c r="H636" t="inlineStr">
         <is>
-          <t>xrf, x-ray fluorescence, phased array, ndt, nde, inspection system, NDT</t>
+          <t>xrf, x-ray fluorescence, phased array, NDT</t>
         </is>
       </c>
       <c r="I636" t="inlineStr">
@@ -26163,26 +25095,14 @@
       <c r="E638" t="n">
         <v>6241</v>
       </c>
-      <c r="F638" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G638" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H638" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I638" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F638" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G638" t="inlineStr"/>
+      <c r="H638" t="inlineStr"/>
+      <c r="I638" t="inlineStr"/>
       <c r="J638" t="inlineStr">
         <is>
           <t>Live</t>
@@ -26220,7 +25140,7 @@
       </c>
       <c r="H639" t="inlineStr">
         <is>
-          <t>ndt, nde, eddy current, NDT</t>
+          <t>eddy current, NDT</t>
         </is>
       </c>
       <c r="I639" t="inlineStr">
@@ -26443,26 +25363,14 @@
       <c r="E645" t="n">
         <v>5714</v>
       </c>
-      <c r="F645" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G645" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H645" t="inlineStr">
-        <is>
-          <t>inspection system</t>
-        </is>
-      </c>
-      <c r="I645" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F645" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G645" t="inlineStr"/>
+      <c r="H645" t="inlineStr"/>
+      <c r="I645" t="inlineStr"/>
       <c r="J645" t="inlineStr">
         <is>
           <t>Live</t>
@@ -26500,12 +25408,12 @@
       </c>
       <c r="G646" t="inlineStr">
         <is>
-          <t>XRF / XRD Analyzers; Remote Visual Inspection (RVI); Non-Destructive Testing (NDT/NDE)</t>
+          <t>XRF / XRD Analyzers; Remote Visual Inspection (RVI)</t>
         </is>
       </c>
       <c r="H646" t="inlineStr">
         <is>
-          <t>xrf, handheld xrf, alloy analysis, Vanta, rvi, nde</t>
+          <t>xrf, handheld xrf, alloy analysis, Vanta, rvi</t>
         </is>
       </c>
       <c r="I646" t="inlineStr">
@@ -26543,26 +25451,14 @@
       <c r="E647" t="n">
         <v>2208</v>
       </c>
-      <c r="F647" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G647" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H647" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I647" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F647" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G647" t="inlineStr"/>
+      <c r="H647" t="inlineStr"/>
+      <c r="I647" t="inlineStr"/>
       <c r="J647" t="inlineStr">
         <is>
           <t>Live</t>
@@ -26593,26 +25489,14 @@
       <c r="E648" t="n">
         <v>2820</v>
       </c>
-      <c r="F648" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G648" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H648" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I648" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F648" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G648" t="inlineStr"/>
+      <c r="H648" t="inlineStr"/>
+      <c r="I648" t="inlineStr"/>
       <c r="J648" t="inlineStr">
         <is>
           <t>Live</t>
@@ -26671,26 +25555,14 @@
       <c r="E650" t="n">
         <v>1574</v>
       </c>
-      <c r="F650" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G650" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H650" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I650" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F650" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G650" t="inlineStr"/>
+      <c r="H650" t="inlineStr"/>
+      <c r="I650" t="inlineStr"/>
       <c r="J650" t="inlineStr">
         <is>
           <t>Live</t>
@@ -26804,12 +25676,12 @@
       </c>
       <c r="G653" t="inlineStr">
         <is>
-          <t>XRF / XRD Analyzers; Remote Visual Inspection (RVI); Ultrasonic Testing (UT); Non-Destructive Testing (NDT/NDE)</t>
+          <t>XRF / XRD Analyzers; Remote Visual Inspection (RVI); Ultrasonic Testing (UT)</t>
         </is>
       </c>
       <c r="H653" t="inlineStr">
         <is>
-          <t>xrf, handheld xrf, Vanta, rvi, EPOCH, nde</t>
+          <t>xrf, handheld xrf, Vanta, rvi, EPOCH</t>
         </is>
       </c>
       <c r="I653" t="inlineStr">
@@ -26999,26 +25871,14 @@
       <c r="E658" t="n">
         <v>292</v>
       </c>
-      <c r="F658" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G658" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H658" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I658" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F658" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G658" t="inlineStr"/>
+      <c r="H658" t="inlineStr"/>
+      <c r="I658" t="inlineStr"/>
       <c r="J658" t="inlineStr">
         <is>
           <t>Live</t>
@@ -27104,7 +25964,7 @@
       <c r="I660" t="inlineStr"/>
       <c r="J660" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -27142,7 +26002,7 @@
       <c r="I661" t="inlineStr"/>
       <c r="J661" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -27172,12 +26032,12 @@
       </c>
       <c r="G662" t="inlineStr">
         <is>
-          <t>XRF / XRD Analyzers; Remote Visual Inspection (RVI); Ultrasonic Testing (UT); Non-Destructive Testing (NDT/NDE); Industrial Videoscopes / Inspection Tools</t>
+          <t>XRF / XRD Analyzers; Remote Visual Inspection (RVI); Ultrasonic Testing (UT); Industrial Videoscopes / Inspection Tools</t>
         </is>
       </c>
       <c r="H662" t="inlineStr">
         <is>
-          <t>xrf, x-ray fluorescence, portable xrf, pxrf, DELTA, remote visual inspection, rvi, videoscope, video borescope, borescope, turbine inspection, IPLEX, phased array, nde, iplex</t>
+          <t>xrf, x-ray fluorescence, portable xrf, pxrf, DELTA, remote visual inspection, rvi, videoscope, video borescope, borescope, turbine inspection, IPLEX, phased array, iplex</t>
         </is>
       </c>
       <c r="I662" t="inlineStr">
@@ -27217,12 +26077,12 @@
       </c>
       <c r="G663" t="inlineStr">
         <is>
-          <t>XRF / XRD Analyzers; Remote Visual Inspection (RVI); Ultrasonic Testing (UT); Non-Destructive Testing (NDT/NDE); Industrial Videoscopes / Inspection Tools</t>
+          <t>XRF / XRD Analyzers; Remote Visual Inspection (RVI); Ultrasonic Testing (UT); Industrial Videoscopes / Inspection Tools</t>
         </is>
       </c>
       <c r="H663" t="inlineStr">
         <is>
-          <t>xrf, x-ray fluorescence, portable xrf, pxrf, DELTA, remote visual inspection, rvi, videoscope, video borescope, borescope, turbine inspection, IPLEX, phased array, nde, iplex</t>
+          <t>xrf, x-ray fluorescence, portable xrf, pxrf, DELTA, remote visual inspection, rvi, videoscope, video borescope, borescope, turbine inspection, IPLEX, phased array, iplex</t>
         </is>
       </c>
       <c r="I663" t="inlineStr">
@@ -27395,7 +26255,7 @@
       </c>
       <c r="H667" t="inlineStr">
         <is>
-          <t>xrf, pmi, ndt, NDT</t>
+          <t>xrf, pmi, NDT</t>
         </is>
       </c>
       <c r="I667" t="inlineStr">
@@ -27440,7 +26300,7 @@
       </c>
       <c r="H668" t="inlineStr">
         <is>
-          <t>rvi, ultrasonic testing, ultrasonic flaw, phased array, weld inspection, flaw detection, nondestructive testing, ndt, nde, eddy current, NDT</t>
+          <t>rvi, ultrasonic testing, ultrasonic flaw, phased array, weld inspection, flaw detection, nondestructive testing, eddy current, NDT</t>
         </is>
       </c>
       <c r="I668" t="inlineStr">
@@ -27627,26 +26487,14 @@
       <c r="E673" t="n">
         <v>3778</v>
       </c>
-      <c r="F673" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G673" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H673" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I673" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F673" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G673" t="inlineStr"/>
+      <c r="H673" t="inlineStr"/>
+      <c r="I673" t="inlineStr"/>
       <c r="J673" t="inlineStr">
         <is>
           <t>Live</t>
@@ -27715,29 +26563,17 @@
       <c r="E675" t="n">
         <v>192</v>
       </c>
-      <c r="F675" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G675" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H675" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I675" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F675" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G675" t="inlineStr"/>
+      <c r="H675" t="inlineStr"/>
+      <c r="I675" t="inlineStr"/>
       <c r="J675" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -27775,7 +26611,7 @@
       <c r="I676" t="inlineStr"/>
       <c r="J676" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -27803,29 +26639,17 @@
       <c r="E677" t="n">
         <v>4988</v>
       </c>
-      <c r="F677" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G677" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H677" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I677" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F677" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G677" t="inlineStr"/>
+      <c r="H677" t="inlineStr"/>
+      <c r="I677" t="inlineStr"/>
       <c r="J677" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -27863,7 +26687,7 @@
       <c r="I678" t="inlineStr"/>
       <c r="J678" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -27891,29 +26715,17 @@
       <c r="E679" t="n">
         <v>5490</v>
       </c>
-      <c r="F679" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G679" t="inlineStr">
-        <is>
-          <t>Ultrasonic Testing (UT)</t>
-        </is>
-      </c>
-      <c r="H679" t="inlineStr">
-        <is>
-          <t>thickness measurement</t>
-        </is>
-      </c>
-      <c r="I679" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F679" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G679" t="inlineStr"/>
+      <c r="H679" t="inlineStr"/>
+      <c r="I679" t="inlineStr"/>
       <c r="J679" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -27981,17 +26793,17 @@
       </c>
       <c r="G681" t="inlineStr">
         <is>
-          <t>Non-Destructive Testing (NDT/NDE); Industrial Videoscopes / Inspection Tools</t>
+          <t>Industrial Videoscopes / Inspection Tools</t>
         </is>
       </c>
       <c r="H681" t="inlineStr">
         <is>
-          <t>ndt, iplex</t>
+          <t>iplex</t>
         </is>
       </c>
       <c r="I681" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J681" t="inlineStr">
@@ -28034,7 +26846,7 @@
       <c r="I682" t="inlineStr"/>
       <c r="J682" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -28072,7 +26884,7 @@
       <c r="I683" t="inlineStr"/>
       <c r="J683" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -28110,7 +26922,7 @@
       <c r="I684" t="inlineStr"/>
       <c r="J684" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -28183,7 +26995,7 @@
       </c>
       <c r="H686" t="inlineStr">
         <is>
-          <t>xrf, x-ray fluorescence, handheld xrf, Vanta, remote visual inspection, rvi, phased array, tofd, time-of-flight diffraction, OmniScan, nondestructive testing, ndt, nde, NDT</t>
+          <t>xrf, x-ray fluorescence, handheld xrf, Vanta, remote visual inspection, rvi, phased array, tofd, time-of-flight diffraction, OmniScan, nondestructive testing, NDT</t>
         </is>
       </c>
       <c r="I686" t="inlineStr">
@@ -29326,7 +28138,7 @@
       <c r="I715" t="inlineStr"/>
       <c r="J715" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -29364,7 +28176,7 @@
       <c r="I716" t="inlineStr"/>
       <c r="J716" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -29490,7 +28302,7 @@
       <c r="I719" t="inlineStr"/>
       <c r="J719" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -29556,26 +28368,14 @@
       <c r="E721" t="n">
         <v>3995</v>
       </c>
-      <c r="F721" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G721" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H721" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I721" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F721" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G721" t="inlineStr"/>
+      <c r="H721" t="inlineStr"/>
+      <c r="I721" t="inlineStr"/>
       <c r="J721" t="inlineStr">
         <is>
           <t>Live</t>
@@ -29656,7 +28456,7 @@
       </c>
       <c r="H723" t="inlineStr">
         <is>
-          <t>xrf, VANTA, borescope, ndt, nde, NDT</t>
+          <t>xrf, VANTA, borescope, NDT</t>
         </is>
       </c>
       <c r="I723" t="inlineStr">
@@ -29838,12 +28638,12 @@
       </c>
       <c r="G728" t="inlineStr">
         <is>
-          <t>Remote Visual Inspection (RVI); Non-Destructive Testing (NDT/NDE); Industrial Videoscopes / Inspection Tools</t>
+          <t>Remote Visual Inspection (RVI); Industrial Videoscopes / Inspection Tools</t>
         </is>
       </c>
       <c r="H728" t="inlineStr">
         <is>
-          <t>remote visual inspection, rvi, videoscope, IPLEX, nde, iplex, insertion tube, IPLEXTM, IPLEX videoscope, IPLEX GX, IPLEX GAir</t>
+          <t>remote visual inspection, rvi, videoscope, IPLEX, iplex, insertion tube, IPLEXTM, IPLEX videoscope, IPLEX GX, IPLEX GAir</t>
         </is>
       </c>
       <c r="I728" t="inlineStr">
@@ -29931,7 +28731,7 @@
       </c>
       <c r="H730" t="inlineStr">
         <is>
-          <t>remote visual inspection, rvi, ndt, NDT</t>
+          <t>remote visual inspection, rvi, NDT</t>
         </is>
       </c>
       <c r="I730" t="inlineStr">
@@ -30187,26 +28987,14 @@
       <c r="E737" t="n">
         <v>783</v>
       </c>
-      <c r="F737" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G737" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H737" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I737" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F737" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G737" t="inlineStr"/>
+      <c r="H737" t="inlineStr"/>
+      <c r="I737" t="inlineStr"/>
       <c r="J737" t="inlineStr">
         <is>
           <t>Live</t>
@@ -30277,17 +29065,17 @@
       </c>
       <c r="G739" t="inlineStr">
         <is>
-          <t>Remote Visual Inspection (RVI); Non-Destructive Testing (NDT/NDE)</t>
+          <t>Remote Visual Inspection (RVI)</t>
         </is>
       </c>
       <c r="H739" t="inlineStr">
         <is>
-          <t>rvi, nde</t>
+          <t>rvi</t>
         </is>
       </c>
       <c r="I739" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J739" t="inlineStr">
@@ -32293,26 +31081,14 @@
       <c r="E792" t="n">
         <v>488</v>
       </c>
-      <c r="F792" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G792" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H792" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I792" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F792" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G792" t="inlineStr"/>
+      <c r="H792" t="inlineStr"/>
+      <c r="I792" t="inlineStr"/>
       <c r="J792" t="inlineStr">
         <is>
           <t>Live</t>
@@ -32669,7 +31445,7 @@
       <c r="I801" t="inlineStr"/>
       <c r="J801" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -32932,17 +31708,17 @@
       </c>
       <c r="G808" t="inlineStr">
         <is>
-          <t>Remote Visual Inspection (RVI); Non-Destructive Testing (NDT/NDE)</t>
+          <t>Remote Visual Inspection (RVI)</t>
         </is>
       </c>
       <c r="H808" t="inlineStr">
         <is>
-          <t>rvi, nde</t>
+          <t>rvi</t>
         </is>
       </c>
       <c r="I808" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J808" t="inlineStr">
@@ -33213,7 +31989,7 @@
       <c r="I815" t="inlineStr"/>
       <c r="J815" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -33711,17 +32487,17 @@
       </c>
       <c r="G828" t="inlineStr">
         <is>
-          <t>Remote Visual Inspection (RVI); Non-Destructive Testing (NDT/NDE)</t>
+          <t>Remote Visual Inspection (RVI)</t>
         </is>
       </c>
       <c r="H828" t="inlineStr">
         <is>
-          <t>rvi, inspection system</t>
+          <t>rvi</t>
         </is>
       </c>
       <c r="I828" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J828" t="inlineStr">
@@ -33756,17 +32532,17 @@
       </c>
       <c r="G829" t="inlineStr">
         <is>
-          <t>Remote Visual Inspection (RVI); Non-Destructive Testing (NDT/NDE)</t>
+          <t>Remote Visual Inspection (RVI)</t>
         </is>
       </c>
       <c r="H829" t="inlineStr">
         <is>
-          <t>rvi, inspection system</t>
+          <t>rvi</t>
         </is>
       </c>
       <c r="I829" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J829" t="inlineStr">
@@ -33801,17 +32577,17 @@
       </c>
       <c r="G830" t="inlineStr">
         <is>
-          <t>Remote Visual Inspection (RVI); Non-Destructive Testing (NDT/NDE)</t>
+          <t>Remote Visual Inspection (RVI)</t>
         </is>
       </c>
       <c r="H830" t="inlineStr">
         <is>
-          <t>rvi, inspection system</t>
+          <t>rvi</t>
         </is>
       </c>
       <c r="I830" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J830" t="inlineStr">
@@ -34034,26 +32810,14 @@
       <c r="E836" t="n">
         <v>1919</v>
       </c>
-      <c r="F836" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G836" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H836" t="inlineStr">
-        <is>
-          <t>inspection system</t>
-        </is>
-      </c>
-      <c r="I836" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F836" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G836" t="inlineStr"/>
+      <c r="H836" t="inlineStr"/>
+      <c r="I836" t="inlineStr"/>
       <c r="J836" t="inlineStr">
         <is>
           <t>Live</t>
@@ -34355,7 +33119,7 @@
       <c r="I844" t="inlineStr"/>
       <c r="J844" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -34383,29 +33147,17 @@
       <c r="E845" t="n">
         <v>196</v>
       </c>
-      <c r="F845" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G845" t="inlineStr">
-        <is>
-          <t>Remote Visual Inspection (RVI)</t>
-        </is>
-      </c>
-      <c r="H845" t="inlineStr">
-        <is>
-          <t>rvi</t>
-        </is>
-      </c>
-      <c r="I845" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F845" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G845" t="inlineStr"/>
+      <c r="H845" t="inlineStr"/>
+      <c r="I845" t="inlineStr"/>
       <c r="J845" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -34557,7 +33309,7 @@
       <c r="I849" t="inlineStr"/>
       <c r="J849" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -34585,29 +33337,17 @@
       <c r="E850" t="n">
         <v>529</v>
       </c>
-      <c r="F850" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G850" t="inlineStr">
-        <is>
-          <t>Remote Visual Inspection (RVI); Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H850" t="inlineStr">
-        <is>
-          <t>rvi, nde</t>
-        </is>
-      </c>
-      <c r="I850" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="F850" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G850" t="inlineStr"/>
+      <c r="H850" t="inlineStr"/>
+      <c r="I850" t="inlineStr"/>
       <c r="J850" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -34721,7 +33461,7 @@
       <c r="I853" t="inlineStr"/>
       <c r="J853" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -34991,17 +33731,17 @@
       </c>
       <c r="G860" t="inlineStr">
         <is>
-          <t>Remote Visual Inspection (RVI); Non-Destructive Testing (NDT/NDE)</t>
+          <t>Remote Visual Inspection (RVI)</t>
         </is>
       </c>
       <c r="H860" t="inlineStr">
         <is>
-          <t>rvi, nde</t>
+          <t>rvi</t>
         </is>
       </c>
       <c r="I860" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J860" t="inlineStr">
@@ -35234,7 +33974,7 @@
       <c r="I866" t="inlineStr"/>
       <c r="J866" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -35386,7 +34126,7 @@
       <c r="I870" t="inlineStr"/>
       <c r="J870" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -35756,26 +34496,14 @@
       <c r="E880" t="n">
         <v>3868</v>
       </c>
-      <c r="F880" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G880" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H880" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I880" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F880" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G880" t="inlineStr"/>
+      <c r="H880" t="inlineStr"/>
+      <c r="I880" t="inlineStr"/>
       <c r="J880" t="inlineStr">
         <is>
           <t>Live</t>
@@ -37240,26 +35968,14 @@
       <c r="E919" t="n">
         <v>1365</v>
       </c>
-      <c r="F919" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G919" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H919" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I919" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F919" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G919" t="inlineStr"/>
+      <c r="H919" t="inlineStr"/>
+      <c r="I919" t="inlineStr"/>
       <c r="J919" t="inlineStr">
         <is>
           <t>Live</t>
@@ -37300,7 +36016,7 @@
       <c r="I920" t="inlineStr"/>
       <c r="J920" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -37376,7 +36092,7 @@
       <c r="I922" t="inlineStr"/>
       <c r="J922" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -37490,7 +36206,7 @@
       <c r="I925" t="inlineStr"/>
       <c r="J925" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -37566,7 +36282,7 @@
       <c r="I927" t="inlineStr"/>
       <c r="J927" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -38321,7 +37037,7 @@
       <c r="I947" t="inlineStr"/>
       <c r="J947" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -38359,7 +37075,7 @@
       <c r="I948" t="inlineStr"/>
       <c r="J948" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -38397,7 +37113,7 @@
       <c r="I949" t="inlineStr"/>
       <c r="J949" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -38425,29 +37141,17 @@
       <c r="E950" t="n">
         <v>5023</v>
       </c>
-      <c r="F950" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G950" t="inlineStr">
-        <is>
-          <t>Remote Visual Inspection (RVI); Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H950" t="inlineStr">
-        <is>
-          <t>rvi, nde</t>
-        </is>
-      </c>
-      <c r="I950" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="F950" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G950" t="inlineStr"/>
+      <c r="H950" t="inlineStr"/>
+      <c r="I950" t="inlineStr"/>
       <c r="J950" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -38485,7 +37189,7 @@
       <c r="I951" t="inlineStr"/>
       <c r="J951" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -38513,29 +37217,17 @@
       <c r="E952" t="n">
         <v>4979</v>
       </c>
-      <c r="F952" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G952" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H952" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I952" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F952" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G952" t="inlineStr"/>
+      <c r="H952" t="inlineStr"/>
+      <c r="I952" t="inlineStr"/>
       <c r="J952" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -38563,29 +37255,17 @@
       <c r="E953" t="n">
         <v>4963</v>
       </c>
-      <c r="F953" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G953" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H953" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I953" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F953" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G953" t="inlineStr"/>
+      <c r="H953" t="inlineStr"/>
+      <c r="I953" t="inlineStr"/>
       <c r="J953" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -38613,29 +37293,17 @@
       <c r="E954" t="n">
         <v>4968</v>
       </c>
-      <c r="F954" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G954" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H954" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I954" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F954" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G954" t="inlineStr"/>
+      <c r="H954" t="inlineStr"/>
+      <c r="I954" t="inlineStr"/>
       <c r="J954" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -38673,7 +37341,7 @@
       <c r="I955" t="inlineStr"/>
       <c r="J955" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -38711,7 +37379,7 @@
       <c r="I956" t="inlineStr"/>
       <c r="J956" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -38739,29 +37407,17 @@
       <c r="E957" t="n">
         <v>4364</v>
       </c>
-      <c r="F957" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G957" t="inlineStr">
-        <is>
-          <t>Remote Visual Inspection (RVI)</t>
-        </is>
-      </c>
-      <c r="H957" t="inlineStr">
-        <is>
-          <t>rvi</t>
-        </is>
-      </c>
-      <c r="I957" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F957" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G957" t="inlineStr"/>
+      <c r="H957" t="inlineStr"/>
+      <c r="I957" t="inlineStr"/>
       <c r="J957" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -38799,7 +37455,7 @@
       <c r="I958" t="inlineStr"/>
       <c r="J958" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -38837,7 +37493,7 @@
       <c r="I959" t="inlineStr"/>
       <c r="J959" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -38875,7 +37531,7 @@
       <c r="I960" t="inlineStr"/>
       <c r="J960" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -38913,7 +37569,7 @@
       <c r="I961" t="inlineStr"/>
       <c r="J961" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -38951,7 +37607,7 @@
       <c r="I962" t="inlineStr"/>
       <c r="J962" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -38989,7 +37645,7 @@
       <c r="I963" t="inlineStr"/>
       <c r="J963" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -39027,7 +37683,7 @@
       <c r="I964" t="inlineStr"/>
       <c r="J964" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -39055,29 +37711,17 @@
       <c r="E965" t="n">
         <v>2221</v>
       </c>
-      <c r="F965" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G965" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H965" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I965" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F965" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G965" t="inlineStr"/>
+      <c r="H965" t="inlineStr"/>
+      <c r="I965" t="inlineStr"/>
       <c r="J965" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -39115,7 +37759,7 @@
       <c r="I966" t="inlineStr"/>
       <c r="J966" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -39153,7 +37797,7 @@
       <c r="I967" t="inlineStr"/>
       <c r="J967" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -39191,7 +37835,7 @@
       <c r="I968" t="inlineStr"/>
       <c r="J968" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -39229,7 +37873,7 @@
       <c r="I969" t="inlineStr"/>
       <c r="J969" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -39267,7 +37911,7 @@
       <c r="I970" t="inlineStr"/>
       <c r="J970" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -39305,7 +37949,7 @@
       <c r="I971" t="inlineStr"/>
       <c r="J971" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -39343,7 +37987,7 @@
       <c r="I972" t="inlineStr"/>
       <c r="J972" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -39495,7 +38139,7 @@
       <c r="I976" t="inlineStr"/>
       <c r="J976" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -39533,7 +38177,7 @@
       <c r="I977" t="inlineStr"/>
       <c r="J977" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -39599,29 +38243,17 @@
       <c r="E979" t="n">
         <v>4268</v>
       </c>
-      <c r="F979" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G979" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H979" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I979" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F979" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G979" t="inlineStr"/>
+      <c r="H979" t="inlineStr"/>
+      <c r="I979" t="inlineStr"/>
       <c r="J979" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -39697,7 +38329,7 @@
       <c r="I981" t="inlineStr"/>
       <c r="J981" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -39735,7 +38367,7 @@
       <c r="I982" t="inlineStr"/>
       <c r="J982" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -39773,7 +38405,7 @@
       <c r="I983" t="inlineStr"/>
       <c r="J983" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -39976,26 +38608,14 @@
       <c r="E989" t="n">
         <v>3767</v>
       </c>
-      <c r="F989" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G989" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H989" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I989" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F989" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G989" t="inlineStr"/>
+      <c r="H989" t="inlineStr"/>
+      <c r="I989" t="inlineStr"/>
       <c r="J989" t="inlineStr">
         <is>
           <t>Live</t>
@@ -40221,7 +38841,7 @@
       <c r="I995" t="inlineStr"/>
       <c r="J995" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -40332,7 +38952,7 @@
       </c>
       <c r="H998" t="inlineStr">
         <is>
-          <t>phased array, OmniScan, ndt, NDT</t>
+          <t>phased array, OmniScan, NDT</t>
         </is>
       </c>
       <c r="I998" t="inlineStr">
@@ -40415,7 +39035,7 @@
       </c>
       <c r="H1000" t="inlineStr">
         <is>
-          <t>nondestructive testing, ndt, nde, NDT</t>
+          <t>nondestructive testing, NDT</t>
         </is>
       </c>
       <c r="I1000" t="inlineStr">
@@ -40543,7 +39163,7 @@
       </c>
       <c r="H1003" t="inlineStr">
         <is>
-          <t>ultrasonic flaw, OmniScan, ndt, NDT</t>
+          <t>ultrasonic flaw, OmniScan, NDT</t>
         </is>
       </c>
       <c r="I1003" t="inlineStr">
@@ -40633,7 +39253,7 @@
       </c>
       <c r="H1005" t="inlineStr">
         <is>
-          <t>ultrasonic flaw, phased array, flaw detection, EPOCH, ndt, nde, NDT</t>
+          <t>ultrasonic flaw, phased array, flaw detection, EPOCH, NDT</t>
         </is>
       </c>
       <c r="I1005" t="inlineStr">
@@ -40673,12 +39293,12 @@
       </c>
       <c r="G1006" t="inlineStr">
         <is>
-          <t>XRF / XRD Analyzers; Non-Destructive Testing (NDT/NDE)</t>
+          <t>XRF / XRD Analyzers</t>
         </is>
       </c>
       <c r="H1006" t="inlineStr">
         <is>
-          <t>xrf, xrd, x-ray diffraction, nde</t>
+          <t>xrf, xrd, x-ray diffraction</t>
         </is>
       </c>
       <c r="I1006" t="inlineStr">
@@ -40718,17 +39338,17 @@
       </c>
       <c r="G1007" t="inlineStr">
         <is>
-          <t>XRF / XRD Analyzers; Non-Destructive Testing (NDT/NDE)</t>
+          <t>XRF / XRD Analyzers</t>
         </is>
       </c>
       <c r="H1007" t="inlineStr">
         <is>
-          <t>xrf, nde</t>
+          <t>xrf</t>
         </is>
       </c>
       <c r="I1007" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J1007" t="inlineStr">
@@ -40853,12 +39473,12 @@
       </c>
       <c r="G1010" t="inlineStr">
         <is>
-          <t>XRF / XRD Analyzers; Remote Visual Inspection (RVI); Non-Destructive Testing (NDT/NDE)</t>
+          <t>XRF / XRD Analyzers; Remote Visual Inspection (RVI)</t>
         </is>
       </c>
       <c r="H1010" t="inlineStr">
         <is>
-          <t>xrf, portable xrf, elemental analysis, rvi, nde</t>
+          <t>xrf, portable xrf, elemental analysis, rvi</t>
         </is>
       </c>
       <c r="I1010" t="inlineStr">
@@ -40898,17 +39518,17 @@
       </c>
       <c r="G1011" t="inlineStr">
         <is>
-          <t>XRF / XRD Analyzers; Non-Destructive Testing (NDT/NDE)</t>
+          <t>XRF / XRD Analyzers</t>
         </is>
       </c>
       <c r="H1011" t="inlineStr">
         <is>
-          <t>xrf, portable xrf, nde</t>
+          <t>xrf, portable xrf</t>
         </is>
       </c>
       <c r="I1011" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J1011" t="inlineStr">
@@ -41026,12 +39646,12 @@
       </c>
       <c r="G1014" t="inlineStr">
         <is>
-          <t>Remote Visual Inspection (RVI); Non-Destructive Testing (NDT/NDE); Industrial Videoscopes / Inspection Tools</t>
+          <t>Remote Visual Inspection (RVI); Industrial Videoscopes / Inspection Tools</t>
         </is>
       </c>
       <c r="H1014" t="inlineStr">
         <is>
-          <t>remote visual inspection, rvi, videoscope, IPLEX, nde, iplex, IPLEX LX, IPLEX LT, IPLEX systems, IPLEX FX, IPLEX units, IPLEX Viewer</t>
+          <t>remote visual inspection, rvi, videoscope, IPLEX, iplex, IPLEX LX, IPLEX LT, IPLEX systems, IPLEX FX, IPLEX units, IPLEX Viewer</t>
         </is>
       </c>
       <c r="I1014" t="inlineStr">
@@ -41076,7 +39696,7 @@
       </c>
       <c r="H1015" t="inlineStr">
         <is>
-          <t>phased array, weld inspection, OmniScan, nondestructive testing, nde</t>
+          <t>phased array, weld inspection, OmniScan, nondestructive testing</t>
         </is>
       </c>
       <c r="I1015" t="inlineStr">
@@ -41121,7 +39741,7 @@
       </c>
       <c r="H1016" t="inlineStr">
         <is>
-          <t>ultrasonic testing, OmniScan, nondestructive testing, nde</t>
+          <t>ultrasonic testing, OmniScan, nondestructive testing</t>
         </is>
       </c>
       <c r="I1016" t="inlineStr">
@@ -41161,17 +39781,17 @@
       </c>
       <c r="G1017" t="inlineStr">
         <is>
-          <t>XRF / XRD Analyzers; Non-Destructive Testing (NDT/NDE)</t>
+          <t>XRF / XRD Analyzers</t>
         </is>
       </c>
       <c r="H1017" t="inlineStr">
         <is>
-          <t>xrf, nde</t>
+          <t>xrf</t>
         </is>
       </c>
       <c r="I1017" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J1017" t="inlineStr">
@@ -41296,12 +39916,12 @@
       </c>
       <c r="G1020" t="inlineStr">
         <is>
-          <t>XRF / XRD Analyzers; Remote Visual Inspection (RVI); Non-Destructive Testing (NDT/NDE)</t>
+          <t>XRF / XRD Analyzers; Remote Visual Inspection (RVI)</t>
         </is>
       </c>
       <c r="H1020" t="inlineStr">
         <is>
-          <t>xrf, portable xrf, elemental analysis, rvi, nde</t>
+          <t>xrf, portable xrf, elemental analysis, rvi</t>
         </is>
       </c>
       <c r="I1020" t="inlineStr">
@@ -41386,12 +40006,12 @@
       </c>
       <c r="G1022" t="inlineStr">
         <is>
-          <t>XRF / XRD Analyzers; Non-Destructive Testing (NDT/NDE)</t>
+          <t>XRF / XRD Analyzers</t>
         </is>
       </c>
       <c r="H1022" t="inlineStr">
         <is>
-          <t>xrf, x-ray fluorescence, portable xrf, nde</t>
+          <t>xrf, x-ray fluorescence, portable xrf</t>
         </is>
       </c>
       <c r="I1022" t="inlineStr">
@@ -41431,17 +40051,17 @@
       </c>
       <c r="G1023" t="inlineStr">
         <is>
-          <t>XRF / XRD Analyzers; Non-Destructive Testing (NDT/NDE)</t>
+          <t>XRF / XRD Analyzers</t>
         </is>
       </c>
       <c r="H1023" t="inlineStr">
         <is>
-          <t>xrd, x-ray diffraction, nde</t>
+          <t>xrd, x-ray diffraction</t>
         </is>
       </c>
       <c r="I1023" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J1023" t="inlineStr">
@@ -41476,12 +40096,12 @@
       </c>
       <c r="G1024" t="inlineStr">
         <is>
-          <t>XRF / XRD Analyzers; Non-Destructive Testing (NDT/NDE)</t>
+          <t>XRF / XRD Analyzers</t>
         </is>
       </c>
       <c r="H1024" t="inlineStr">
         <is>
-          <t>xrf, x-ray fluorescence, portable xrf, pxrf, nde</t>
+          <t>xrf, x-ray fluorescence, portable xrf, pxrf</t>
         </is>
       </c>
       <c r="I1024" t="inlineStr">
@@ -41521,17 +40141,17 @@
       </c>
       <c r="G1025" t="inlineStr">
         <is>
-          <t>XRF / XRD Analyzers; Non-Destructive Testing (NDT/NDE)</t>
+          <t>XRF / XRD Analyzers</t>
         </is>
       </c>
       <c r="H1025" t="inlineStr">
         <is>
-          <t>xrf, x-ray fluorescence, nde</t>
+          <t>xrf, x-ray fluorescence</t>
         </is>
       </c>
       <c r="I1025" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J1025" t="inlineStr">
@@ -41649,12 +40269,12 @@
       </c>
       <c r="G1028" t="inlineStr">
         <is>
-          <t>Remote Visual Inspection (RVI); Non-Destructive Testing (NDT/NDE); Industrial Videoscopes / Inspection Tools</t>
+          <t>Remote Visual Inspection (RVI); Industrial Videoscopes / Inspection Tools</t>
         </is>
       </c>
       <c r="H1028" t="inlineStr">
         <is>
-          <t>videoscope, IPLEX, nde, iplex, IPLEX LX, IPLEX LT, IPLEX systems, IPLEX Viewer</t>
+          <t>videoscope, IPLEX, iplex, IPLEX LX, IPLEX LT, IPLEX systems, IPLEX Viewer</t>
         </is>
       </c>
       <c r="I1028" t="inlineStr">
@@ -41699,7 +40319,7 @@
       </c>
       <c r="H1029" t="inlineStr">
         <is>
-          <t>thickness measurement, wall thickness, nondestructive testing, ndt, nde, NDT</t>
+          <t>thickness measurement, wall thickness, nondestructive testing, NDT</t>
         </is>
       </c>
       <c r="I1029" t="inlineStr">
@@ -41744,7 +40364,7 @@
       </c>
       <c r="H1030" t="inlineStr">
         <is>
-          <t>ultrasonic flaw, flaw detection, EPOCH, nondestructive testing, ndt, nde, NDT</t>
+          <t>ultrasonic flaw, flaw detection, EPOCH, nondestructive testing, NDT</t>
         </is>
       </c>
       <c r="I1030" t="inlineStr">
@@ -41789,7 +40409,7 @@
       </c>
       <c r="H1031" t="inlineStr">
         <is>
-          <t>xrf, x-ray fluorescence, innovx, remote visual inspection, videoscope, nondestructive testing, ndt, nde, eddy current, NDT</t>
+          <t>xrf, x-ray fluorescence, innovx, remote visual inspection, videoscope, nondestructive testing, eddy current, NDT</t>
         </is>
       </c>
       <c r="I1031" t="inlineStr">
@@ -41834,7 +40454,7 @@
       </c>
       <c r="H1032" t="inlineStr">
         <is>
-          <t>phased array, OmniScan, nondestructive testing, ndt, nde, NDT</t>
+          <t>phased array, OmniScan, nondestructive testing, NDT</t>
         </is>
       </c>
       <c r="I1032" t="inlineStr">
@@ -41879,17 +40499,17 @@
       </c>
       <c r="G1033" t="inlineStr">
         <is>
-          <t>Remote Visual Inspection (RVI); Non-Destructive Testing (NDT/NDE); Industrial Videoscopes / Inspection Tools</t>
+          <t>Remote Visual Inspection (RVI); Industrial Videoscopes / Inspection Tools</t>
         </is>
       </c>
       <c r="H1033" t="inlineStr">
         <is>
-          <t>borescope, nde, insertion tube</t>
+          <t>borescope, insertion tube</t>
         </is>
       </c>
       <c r="I1033" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J1033" t="inlineStr">
@@ -41924,12 +40544,12 @@
       </c>
       <c r="G1034" t="inlineStr">
         <is>
-          <t>Remote Visual Inspection (RVI); Non-Destructive Testing (NDT/NDE); Industrial Videoscopes / Inspection Tools</t>
+          <t>Remote Visual Inspection (RVI); Industrial Videoscopes / Inspection Tools</t>
         </is>
       </c>
       <c r="H1034" t="inlineStr">
         <is>
-          <t>remote visual inspection, rvi, videoscope, IPLEX, nde, iplex, insertion tube, IPLEX YS, IPLEX technology, IPLEX FX</t>
+          <t>remote visual inspection, rvi, videoscope, IPLEX, iplex, insertion tube, IPLEX YS, IPLEX technology, IPLEX FX</t>
         </is>
       </c>
       <c r="I1034" t="inlineStr">
@@ -41969,12 +40589,12 @@
       </c>
       <c r="G1035" t="inlineStr">
         <is>
-          <t>XRF / XRD Analyzers; Non-Destructive Testing (NDT/NDE)</t>
+          <t>XRF / XRD Analyzers</t>
         </is>
       </c>
       <c r="H1035" t="inlineStr">
         <is>
-          <t>xrf, handheld xrf, DELTA, nde</t>
+          <t>xrf, handheld xrf, DELTA</t>
         </is>
       </c>
       <c r="I1035" t="inlineStr">
@@ -42104,12 +40724,12 @@
       </c>
       <c r="G1038" t="inlineStr">
         <is>
-          <t>XRF / XRD Analyzers; Non-Destructive Testing (NDT/NDE)</t>
+          <t>XRF / XRD Analyzers</t>
         </is>
       </c>
       <c r="H1038" t="inlineStr">
         <is>
-          <t>xrf, x-ray fluorescence, portable xrf, elemental analysis, nde</t>
+          <t>xrf, x-ray fluorescence, portable xrf, elemental analysis</t>
         </is>
       </c>
       <c r="I1038" t="inlineStr">
@@ -42149,12 +40769,12 @@
       </c>
       <c r="G1039" t="inlineStr">
         <is>
-          <t>XRF / XRD Analyzers; Non-Destructive Testing (NDT/NDE)</t>
+          <t>XRF / XRD Analyzers</t>
         </is>
       </c>
       <c r="H1039" t="inlineStr">
         <is>
-          <t>xrf, x-ray fluorescence, xrd, handheld xrf, portable xrf, DELTA, nde</t>
+          <t>xrf, x-ray fluorescence, xrd, handheld xrf, portable xrf, DELTA</t>
         </is>
       </c>
       <c r="I1039" t="inlineStr">
@@ -42282,7 +40902,7 @@
       </c>
       <c r="H1042" t="inlineStr">
         <is>
-          <t>phased array, wall thickness, ndt, inspection system, NDT</t>
+          <t>phased array, wall thickness, NDT</t>
         </is>
       </c>
       <c r="I1042" t="inlineStr">
@@ -42322,12 +40942,12 @@
       </c>
       <c r="G1043" t="inlineStr">
         <is>
-          <t>XRF / XRD Analyzers; Non-Destructive Testing (NDT/NDE)</t>
+          <t>XRF / XRD Analyzers</t>
         </is>
       </c>
       <c r="H1043" t="inlineStr">
         <is>
-          <t>xrf, xrd, handheld xrf, Delta, DELTA, delta, nde</t>
+          <t>xrf, xrd, handheld xrf, Delta, DELTA, delta</t>
         </is>
       </c>
       <c r="I1043" t="inlineStr">
@@ -42367,12 +40987,12 @@
       </c>
       <c r="G1044" t="inlineStr">
         <is>
-          <t>XRF / XRD Analyzers; Non-Destructive Testing (NDT/NDE)</t>
+          <t>XRF / XRD Analyzers</t>
         </is>
       </c>
       <c r="H1044" t="inlineStr">
         <is>
-          <t>xrf, xrd, x-ray diffraction, nde</t>
+          <t>xrf, xrd, x-ray diffraction</t>
         </is>
       </c>
       <c r="I1044" t="inlineStr">
@@ -42412,17 +41032,17 @@
       </c>
       <c r="G1045" t="inlineStr">
         <is>
-          <t>XRF / XRD Analyzers; Non-Destructive Testing (NDT/NDE)</t>
+          <t>XRF / XRD Analyzers</t>
         </is>
       </c>
       <c r="H1045" t="inlineStr">
         <is>
-          <t>xrf, xrd, nde</t>
+          <t>xrf, xrd</t>
         </is>
       </c>
       <c r="I1045" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J1045" t="inlineStr">
@@ -42462,7 +41082,7 @@
       </c>
       <c r="H1046" t="inlineStr">
         <is>
-          <t>phased array, tofd, time-of-flight diffraction, OMNISCAN, OmniScan, ndt, NDT</t>
+          <t>phased array, tofd, time-of-flight diffraction, OMNISCAN, OmniScan, NDT</t>
         </is>
       </c>
       <c r="I1046" t="inlineStr">
@@ -42573,12 +41193,12 @@
       </c>
       <c r="G1049" t="inlineStr">
         <is>
-          <t>XRF / XRD Analyzers; Non-Destructive Testing (NDT/NDE)</t>
+          <t>XRF / XRD Analyzers</t>
         </is>
       </c>
       <c r="H1049" t="inlineStr">
         <is>
-          <t>xrf, handheld xrf, portable xrf, pxrf, DELTA, nde</t>
+          <t>xrf, handheld xrf, portable xrf, pxrf, DELTA</t>
         </is>
       </c>
       <c r="I1049" t="inlineStr">
@@ -42723,7 +41343,7 @@
       </c>
       <c r="H1052" t="inlineStr">
         <is>
-          <t>ultrasonic flaw, phased array, weld inspection, EPOCH, nondestructive testing, ndt, nde, NDT</t>
+          <t>ultrasonic flaw, phased array, weld inspection, EPOCH, nondestructive testing, NDT</t>
         </is>
       </c>
       <c r="I1052" t="inlineStr">
@@ -42763,12 +41383,12 @@
       </c>
       <c r="G1053" t="inlineStr">
         <is>
-          <t>XRF / XRD Analyzers; Non-Destructive Testing (NDT/NDE)</t>
+          <t>XRF / XRD Analyzers</t>
         </is>
       </c>
       <c r="H1053" t="inlineStr">
         <is>
-          <t>xrf, xrd, handheld xrf, portable xrf, DELTA, delta, nde</t>
+          <t>xrf, xrd, handheld xrf, portable xrf, DELTA, delta</t>
         </is>
       </c>
       <c r="I1053" t="inlineStr">
@@ -42813,7 +41433,7 @@
       </c>
       <c r="H1054" t="inlineStr">
         <is>
-          <t>xrf, x-ray fluorescence, pmi, ultrasonic flaw, flaw detection, nondestructive testing, ndt, nde, NDT</t>
+          <t>xrf, x-ray fluorescence, pmi, ultrasonic flaw, flaw detection, nondestructive testing, NDT</t>
         </is>
       </c>
       <c r="I1054" t="inlineStr">
@@ -42853,12 +41473,12 @@
       </c>
       <c r="G1055" t="inlineStr">
         <is>
-          <t>XRF / XRD Analyzers; Non-Destructive Testing (NDT/NDE)</t>
+          <t>XRF / XRD Analyzers</t>
         </is>
       </c>
       <c r="H1055" t="inlineStr">
         <is>
-          <t>xrf, x-ray fluorescence, portable xrf, innovx, nde</t>
+          <t>xrf, x-ray fluorescence, portable xrf, innovx</t>
         </is>
       </c>
       <c r="I1055" t="inlineStr">
@@ -43019,7 +41639,7 @@
       </c>
       <c r="H1059" t="inlineStr">
         <is>
-          <t>phased array, weld inspection, OmniScan, nondestructive testing, ndt, nde, NDT</t>
+          <t>phased array, weld inspection, OmniScan, nondestructive testing, NDT</t>
         </is>
       </c>
       <c r="I1059" t="inlineStr">
@@ -43064,7 +41684,7 @@
       </c>
       <c r="H1060" t="inlineStr">
         <is>
-          <t>xrf, xrd, handheld xrf, DELTA, innovx, ndt, nde, NDT</t>
+          <t>xrf, xrd, handheld xrf, DELTA, innovx, NDT</t>
         </is>
       </c>
       <c r="I1060" t="inlineStr">
@@ -43104,12 +41724,12 @@
       </c>
       <c r="G1061" t="inlineStr">
         <is>
-          <t>Remote Visual Inspection (RVI); Non-Destructive Testing (NDT/NDE); Industrial Videoscopes / Inspection Tools</t>
+          <t>Remote Visual Inspection (RVI); Industrial Videoscopes / Inspection Tools</t>
         </is>
       </c>
       <c r="H1061" t="inlineStr">
         <is>
-          <t>remote visual inspection, videoscope, fiberscope, IPLEX, nde, iplex, insertion tube, IPLEX TX</t>
+          <t>remote visual inspection, videoscope, fiberscope, IPLEX, iplex, insertion tube, IPLEX TX</t>
         </is>
       </c>
       <c r="I1061" t="inlineStr">
@@ -43154,7 +41774,7 @@
       </c>
       <c r="H1062" t="inlineStr">
         <is>
-          <t>xrf, xrd, innovx, ndt, nde, NDT</t>
+          <t>xrf, xrd, innovx, NDT</t>
         </is>
       </c>
       <c r="I1062" t="inlineStr">
@@ -43199,7 +41819,7 @@
       </c>
       <c r="H1063" t="inlineStr">
         <is>
-          <t>thickness measurement, nondestructive testing, ndt, nde, NDT</t>
+          <t>thickness measurement, nondestructive testing, NDT</t>
         </is>
       </c>
       <c r="I1063" t="inlineStr">
@@ -43244,7 +41864,7 @@
       </c>
       <c r="H1064" t="inlineStr">
         <is>
-          <t>thickness measurement, wall thickness, nondestructive testing, ndt, nde, NDT</t>
+          <t>thickness measurement, wall thickness, nondestructive testing, NDT</t>
         </is>
       </c>
       <c r="I1064" t="inlineStr">
@@ -43334,7 +41954,7 @@
       </c>
       <c r="H1066" t="inlineStr">
         <is>
-          <t>rvi, ultrasonic testing, phased array, tofd, time-of-flight diffraction, OmniScan, nondestructive testing, ndt, nde, NDT</t>
+          <t>rvi, ultrasonic testing, phased array, tofd, time-of-flight diffraction, OmniScan, nondestructive testing, NDT</t>
         </is>
       </c>
       <c r="I1066" t="inlineStr">
@@ -43412,7 +42032,7 @@
       </c>
       <c r="H1068" t="inlineStr">
         <is>
-          <t>xrf, x-ray fluorescence, xrd, handheld xrf, DELTA, delta, ndt, NDT</t>
+          <t>xrf, x-ray fluorescence, xrd, handheld xrf, DELTA, delta, NDT</t>
         </is>
       </c>
       <c r="I1068" t="inlineStr">
@@ -43457,7 +42077,7 @@
       </c>
       <c r="H1069" t="inlineStr">
         <is>
-          <t>xrf, x-ray fluorescence, xrd, x-ray diffraction, handheld xrf, portable xrf, DELTA, delta, ndt, NDT</t>
+          <t>xrf, x-ray fluorescence, xrd, x-ray diffraction, handheld xrf, portable xrf, DELTA, delta, NDT</t>
         </is>
       </c>
       <c r="I1069" t="inlineStr">
@@ -43502,7 +42122,7 @@
       </c>
       <c r="H1070" t="inlineStr">
         <is>
-          <t>phased array, tofd, OmniScan, ndt, NDT</t>
+          <t>phased array, tofd, OmniScan, NDT</t>
         </is>
       </c>
       <c r="I1070" t="inlineStr">
@@ -43547,7 +42167,7 @@
       </c>
       <c r="H1071" t="inlineStr">
         <is>
-          <t>xrf, x-ray fluorescence, xrd, handheld xrf, DELTA, delta, ndt, NDT</t>
+          <t>xrf, x-ray fluorescence, xrd, handheld xrf, DELTA, delta, NDT</t>
         </is>
       </c>
       <c r="I1071" t="inlineStr">
@@ -43630,7 +42250,7 @@
       </c>
       <c r="H1073" t="inlineStr">
         <is>
-          <t>xrf, x-ray fluorescence, xrd, handheld xrf, DELTA, delta, ndt, nde, NDT</t>
+          <t>xrf, x-ray fluorescence, xrd, handheld xrf, DELTA, delta, NDT</t>
         </is>
       </c>
       <c r="I1073" t="inlineStr">
@@ -43670,17 +42290,17 @@
       </c>
       <c r="G1074" t="inlineStr">
         <is>
-          <t>XRF / XRD Analyzers; Non-Destructive Testing (NDT/NDE)</t>
+          <t>XRF / XRD Analyzers</t>
         </is>
       </c>
       <c r="H1074" t="inlineStr">
         <is>
-          <t>pmi, ndt, nde</t>
+          <t>pmi</t>
         </is>
       </c>
       <c r="I1074" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J1074" t="inlineStr">
@@ -43855,12 +42475,12 @@
       </c>
       <c r="G1078" t="inlineStr">
         <is>
-          <t>Remote Visual Inspection (RVI); Non-Destructive Testing (NDT/NDE); Industrial Videoscopes / Inspection Tools</t>
+          <t>Remote Visual Inspection (RVI); Industrial Videoscopes / Inspection Tools</t>
         </is>
       </c>
       <c r="H1078" t="inlineStr">
         <is>
-          <t>remote visual inspection, videoscope, IPLEX, nde, iplex, IPLEX UltraLite</t>
+          <t>remote visual inspection, videoscope, IPLEX, iplex, IPLEX UltraLite</t>
         </is>
       </c>
       <c r="I1078" t="inlineStr">
@@ -43900,17 +42520,17 @@
       </c>
       <c r="G1079" t="inlineStr">
         <is>
-          <t>Non-Destructive Testing (NDT/NDE); Industrial Videoscopes / Inspection Tools</t>
+          <t>Industrial Videoscopes / Inspection Tools</t>
         </is>
       </c>
       <c r="H1079" t="inlineStr">
         <is>
-          <t>nde, 3d measurement</t>
+          <t>3d measurement</t>
         </is>
       </c>
       <c r="I1079" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J1079" t="inlineStr">
@@ -43945,17 +42565,17 @@
       </c>
       <c r="G1080" t="inlineStr">
         <is>
-          <t>Non-Destructive Testing (NDT/NDE); Industrial Videoscopes / Inspection Tools</t>
+          <t>Industrial Videoscopes / Inspection Tools</t>
         </is>
       </c>
       <c r="H1080" t="inlineStr">
         <is>
-          <t>nde, 3d measurement</t>
+          <t>3d measurement</t>
         </is>
       </c>
       <c r="I1080" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J1080" t="inlineStr">
@@ -44040,7 +42660,7 @@
       </c>
       <c r="H1082" t="inlineStr">
         <is>
-          <t>phased array, tofd, time-of-flight diffraction, weld inspection, OmniScan, ndt, NDT</t>
+          <t>phased array, tofd, time-of-flight diffraction, weld inspection, OmniScan, NDT</t>
         </is>
       </c>
       <c r="I1082" t="inlineStr">
@@ -44085,7 +42705,7 @@
       </c>
       <c r="H1083" t="inlineStr">
         <is>
-          <t>ultrasonic flaw, thickness measurement, corrosion measurement, flaw detection, EPOCH, nondestructive testing, nde</t>
+          <t>ultrasonic flaw, thickness measurement, corrosion measurement, flaw detection, EPOCH, nondestructive testing</t>
         </is>
       </c>
       <c r="I1083" t="inlineStr">
@@ -44130,7 +42750,7 @@
       </c>
       <c r="H1084" t="inlineStr">
         <is>
-          <t>OmniScan, nondestructive testing, ndt, nde, eddy current, magnetic particle, NDT</t>
+          <t>OmniScan, nondestructive testing, eddy current, magnetic particle, NDT</t>
         </is>
       </c>
       <c r="I1084" t="inlineStr">
@@ -44170,12 +42790,12 @@
       </c>
       <c r="G1085" t="inlineStr">
         <is>
-          <t>XRF / XRD Analyzers; Non-Destructive Testing (NDT/NDE)</t>
+          <t>XRF / XRD Analyzers</t>
         </is>
       </c>
       <c r="H1085" t="inlineStr">
         <is>
-          <t>xrf, x-ray fluorescence, xrd, portable xrf, Xpert, xpert, nde</t>
+          <t>xrf, x-ray fluorescence, xrd, portable xrf, Xpert, xpert</t>
         </is>
       </c>
       <c r="I1085" t="inlineStr">
@@ -44215,12 +42835,12 @@
       </c>
       <c r="G1086" t="inlineStr">
         <is>
-          <t>Remote Visual Inspection (RVI); Non-Destructive Testing (NDT/NDE); Industrial Videoscopes / Inspection Tools</t>
+          <t>Remote Visual Inspection (RVI); Industrial Videoscopes / Inspection Tools</t>
         </is>
       </c>
       <c r="H1086" t="inlineStr">
         <is>
-          <t>remote visual inspection, videoscope, IPLEX, nde, iplex, IPLEX RX, IPLEX RT, IPLEX scopes</t>
+          <t>remote visual inspection, videoscope, IPLEX, iplex, IPLEX RX, IPLEX RT, IPLEX scopes</t>
         </is>
       </c>
       <c r="I1086" t="inlineStr">
@@ -44265,7 +42885,7 @@
       </c>
       <c r="H1087" t="inlineStr">
         <is>
-          <t>xrf, handheld xrf, DELTA, ndt, NDT</t>
+          <t>xrf, handheld xrf, DELTA, NDT</t>
         </is>
       </c>
       <c r="I1087" t="inlineStr">
@@ -44348,7 +42968,7 @@
       </c>
       <c r="H1089" t="inlineStr">
         <is>
-          <t>rvi, ndt, nde, inspection system, NDT</t>
+          <t>rvi, NDT</t>
         </is>
       </c>
       <c r="I1089" t="inlineStr">
@@ -44433,12 +43053,12 @@
       </c>
       <c r="G1091" t="inlineStr">
         <is>
-          <t>XRF / XRD Analyzers; Non-Destructive Testing (NDT/NDE)</t>
+          <t>XRF / XRD Analyzers</t>
         </is>
       </c>
       <c r="H1091" t="inlineStr">
         <is>
-          <t>xrf, x-ray fluorescence, xrd, handheld xrf, DELTA, delta, nde</t>
+          <t>xrf, x-ray fluorescence, xrd, handheld xrf, DELTA, delta</t>
         </is>
       </c>
       <c r="I1091" t="inlineStr">
@@ -44483,7 +43103,7 @@
       </c>
       <c r="H1092" t="inlineStr">
         <is>
-          <t>thickness measurement, weld inspection, flaw detection, nondestructive testing, nde, eddy current</t>
+          <t>thickness measurement, weld inspection, flaw detection, nondestructive testing, eddy current</t>
         </is>
       </c>
       <c r="I1092" t="inlineStr">
@@ -44523,12 +43143,12 @@
       </c>
       <c r="G1093" t="inlineStr">
         <is>
-          <t>Remote Visual Inspection (RVI); Non-Destructive Testing (NDT/NDE); Industrial Videoscopes / Inspection Tools</t>
+          <t>Remote Visual Inspection (RVI); Industrial Videoscopes / Inspection Tools</t>
         </is>
       </c>
       <c r="H1093" t="inlineStr">
         <is>
-          <t>remote visual inspection, videoscope, IPLEX, nde, iplex, insertion tube, IPLEX RX</t>
+          <t>remote visual inspection, videoscope, IPLEX, iplex, insertion tube, IPLEX RX</t>
         </is>
       </c>
       <c r="I1093" t="inlineStr">
@@ -44573,7 +43193,7 @@
       </c>
       <c r="H1094" t="inlineStr">
         <is>
-          <t>ultrasonic testing, phased array, OmniScan, nondestructive testing, ndt, nde, NDT</t>
+          <t>ultrasonic testing, phased array, OmniScan, nondestructive testing, NDT</t>
         </is>
       </c>
       <c r="I1094" t="inlineStr">
@@ -44701,12 +43321,12 @@
       </c>
       <c r="H1097" t="inlineStr">
         <is>
-          <t>rvi, nondestructive testing, nde</t>
+          <t>rvi, nondestructive testing</t>
         </is>
       </c>
       <c r="I1097" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J1097" t="inlineStr">
@@ -44767,26 +43387,14 @@
       <c r="E1099" t="n">
         <v>576</v>
       </c>
-      <c r="F1099" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G1099" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H1099" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I1099" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F1099" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G1099" t="inlineStr"/>
+      <c r="H1099" t="inlineStr"/>
+      <c r="I1099" t="inlineStr"/>
       <c r="J1099" t="inlineStr">
         <is>
           <t>Live</t>
@@ -44812,26 +43420,14 @@
       <c r="E1100" t="n">
         <v>5659</v>
       </c>
-      <c r="F1100" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G1100" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H1100" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I1100" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F1100" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G1100" t="inlineStr"/>
+      <c r="H1100" t="inlineStr"/>
+      <c r="I1100" t="inlineStr"/>
       <c r="J1100" t="inlineStr">
         <is>
           <t>Live</t>
@@ -44907,7 +43503,7 @@
       </c>
       <c r="H1102" t="inlineStr">
         <is>
-          <t>remote visual inspection, phased array, OmniScan, nondestructive testing, nde, eddy current</t>
+          <t>remote visual inspection, phased array, OmniScan, nondestructive testing, eddy current</t>
         </is>
       </c>
       <c r="I1102" t="inlineStr">
@@ -44940,26 +43536,14 @@
       <c r="E1103" t="n">
         <v>4992</v>
       </c>
-      <c r="F1103" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G1103" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H1103" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I1103" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F1103" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G1103" t="inlineStr"/>
+      <c r="H1103" t="inlineStr"/>
+      <c r="I1103" t="inlineStr"/>
       <c r="J1103" t="inlineStr">
         <is>
           <t>Live</t>
@@ -44997,7 +43581,7 @@
       </c>
       <c r="H1104" t="inlineStr">
         <is>
-          <t>ultrasonic flaw, phased array, flaw detection, EPOCH, nondestructive testing, nde</t>
+          <t>ultrasonic flaw, phased array, flaw detection, EPOCH, nondestructive testing</t>
         </is>
       </c>
       <c r="I1104" t="inlineStr">
@@ -45130,7 +43714,7 @@
       </c>
       <c r="H1107" t="inlineStr">
         <is>
-          <t>phased array, weld inspection, OmniScan, nondestructive testing, ndt, nde, NDT</t>
+          <t>phased array, weld inspection, OmniScan, nondestructive testing, NDT</t>
         </is>
       </c>
       <c r="I1107" t="inlineStr">
@@ -45175,7 +43759,7 @@
       </c>
       <c r="H1108" t="inlineStr">
         <is>
-          <t>phased array, wall thickness, OmniScan, nondestructive testing, nde</t>
+          <t>phased array, wall thickness, OmniScan, nondestructive testing</t>
         </is>
       </c>
       <c r="I1108" t="inlineStr">
@@ -45220,12 +43804,12 @@
       </c>
       <c r="H1109" t="inlineStr">
         <is>
-          <t>wall thickness, nondestructive testing, nde</t>
+          <t>wall thickness, nondestructive testing</t>
         </is>
       </c>
       <c r="I1109" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J1109" t="inlineStr">
@@ -45324,26 +43908,14 @@
       <c r="E1112" t="n">
         <v>3386</v>
       </c>
-      <c r="F1112" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G1112" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H1112" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I1112" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F1112" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G1112" t="inlineStr"/>
+      <c r="H1112" t="inlineStr"/>
+      <c r="I1112" t="inlineStr"/>
       <c r="J1112" t="inlineStr">
         <is>
           <t>Live</t>
@@ -45376,12 +43948,12 @@
       </c>
       <c r="G1113" t="inlineStr">
         <is>
-          <t>Remote Visual Inspection (RVI); Non-Destructive Testing (NDT/NDE); Industrial Videoscopes / Inspection Tools</t>
+          <t>Remote Visual Inspection (RVI); Industrial Videoscopes / Inspection Tools</t>
         </is>
       </c>
       <c r="H1113" t="inlineStr">
         <is>
-          <t>videoscope, IPLEX, nde, iplex, insertion tube, IPLEX NX, IPLEX NX, IPLEX series</t>
+          <t>videoscope, IPLEX, iplex, insertion tube, IPLEX NX, IPLEX NX, IPLEX series</t>
         </is>
       </c>
       <c r="I1113" t="inlineStr">
@@ -45426,12 +43998,12 @@
       </c>
       <c r="H1114" t="inlineStr">
         <is>
-          <t>rvi, nondestructive testing, nde</t>
+          <t>rvi, nondestructive testing</t>
         </is>
       </c>
       <c r="I1114" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J1114" t="inlineStr">
@@ -45471,12 +44043,12 @@
       </c>
       <c r="H1115" t="inlineStr">
         <is>
-          <t>rvi, nondestructive testing, nde</t>
+          <t>rvi, nondestructive testing</t>
         </is>
       </c>
       <c r="I1115" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J1115" t="inlineStr">
@@ -45556,12 +44128,12 @@
       </c>
       <c r="G1117" t="inlineStr">
         <is>
-          <t>XRF / XRD Analyzers; Non-Destructive Testing (NDT/NDE)</t>
+          <t>XRF / XRD Analyzers</t>
         </is>
       </c>
       <c r="H1117" t="inlineStr">
         <is>
-          <t>xrf, x-ray fluorescence, portable xrf, VANTA, Vanta, nde</t>
+          <t>xrf, x-ray fluorescence, portable xrf, VANTA, Vanta</t>
         </is>
       </c>
       <c r="I1117" t="inlineStr">
@@ -45667,17 +44239,17 @@
       </c>
       <c r="G1120" t="inlineStr">
         <is>
-          <t>Remote Visual Inspection (RVI); Non-Destructive Testing (NDT/NDE)</t>
+          <t>Remote Visual Inspection (RVI)</t>
         </is>
       </c>
       <c r="H1120" t="inlineStr">
         <is>
-          <t>rvi, inspection system</t>
+          <t>rvi</t>
         </is>
       </c>
       <c r="I1120" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J1120" t="inlineStr">
@@ -45743,26 +44315,14 @@
       <c r="E1122" t="n">
         <v>3603</v>
       </c>
-      <c r="F1122" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G1122" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H1122" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I1122" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F1122" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G1122" t="inlineStr"/>
+      <c r="H1122" t="inlineStr"/>
+      <c r="I1122" t="inlineStr"/>
       <c r="J1122" t="inlineStr">
         <is>
           <t>Live</t>
@@ -45840,12 +44400,12 @@
       </c>
       <c r="G1124" t="inlineStr">
         <is>
-          <t>XRF / XRD Analyzers; Non-Destructive Testing (NDT/NDE)</t>
+          <t>XRF / XRD Analyzers</t>
         </is>
       </c>
       <c r="H1124" t="inlineStr">
         <is>
-          <t>xrf, x-ray fluorescence, handheld xrf, Vanta, nde</t>
+          <t>xrf, x-ray fluorescence, handheld xrf, Vanta</t>
         </is>
       </c>
       <c r="I1124" t="inlineStr">
@@ -45963,12 +44523,12 @@
       </c>
       <c r="G1127" t="inlineStr">
         <is>
-          <t>Ultrasonic Testing (UT); Non-Destructive Testing (NDT/NDE)</t>
+          <t>Ultrasonic Testing (UT)</t>
         </is>
       </c>
       <c r="H1127" t="inlineStr">
         <is>
-          <t>ultrasonic inspection, flaw detection, EPOCH, nde</t>
+          <t>ultrasonic inspection, flaw detection, EPOCH</t>
         </is>
       </c>
       <c r="I1127" t="inlineStr">
@@ -46091,26 +44651,14 @@
       <c r="E1130" t="n">
         <v>842</v>
       </c>
-      <c r="F1130" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G1130" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H1130" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I1130" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F1130" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G1130" t="inlineStr"/>
+      <c r="H1130" t="inlineStr"/>
+      <c r="I1130" t="inlineStr"/>
       <c r="J1130" t="inlineStr">
         <is>
           <t>Live</t>
@@ -46136,26 +44684,14 @@
       <c r="E1131" t="n">
         <v>386</v>
       </c>
-      <c r="F1131" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G1131" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H1131" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I1131" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F1131" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G1131" t="inlineStr"/>
+      <c r="H1131" t="inlineStr"/>
+      <c r="I1131" t="inlineStr"/>
       <c r="J1131" t="inlineStr">
         <is>
           <t>Live</t>
@@ -46193,7 +44729,7 @@
       </c>
       <c r="H1132" t="inlineStr">
         <is>
-          <t>remote visual inspection, rvi, videoscope, non-destructive testing, ndt, NDT</t>
+          <t>remote visual inspection, rvi, videoscope, non-destructive testing, NDT</t>
         </is>
       </c>
       <c r="I1132" t="inlineStr">
@@ -46406,12 +44942,12 @@
       </c>
       <c r="G1137" t="inlineStr">
         <is>
-          <t>Remote Visual Inspection (RVI); Non-Destructive Testing (NDT/NDE); Industrial Videoscopes / Inspection Tools</t>
+          <t>Remote Visual Inspection (RVI); Industrial Videoscopes / Inspection Tools</t>
         </is>
       </c>
       <c r="H1137" t="inlineStr">
         <is>
-          <t>videoscope, IPLEX, nde, iplex, IPLEX G, IPLEX series, IPLEX UltraLite</t>
+          <t>videoscope, IPLEX, iplex, IPLEX G, IPLEX series, IPLEX UltraLite</t>
         </is>
       </c>
       <c r="I1137" t="inlineStr">
@@ -46451,12 +44987,12 @@
       </c>
       <c r="G1138" t="inlineStr">
         <is>
-          <t>Remote Visual Inspection (RVI); Non-Destructive Testing (NDT/NDE); Industrial Videoscopes / Inspection Tools</t>
+          <t>Remote Visual Inspection (RVI); Industrial Videoscopes / Inspection Tools</t>
         </is>
       </c>
       <c r="H1138" t="inlineStr">
         <is>
-          <t>videoscope, IPLEX, nde, iplex, IPLEX G, IPLEX UltraLite</t>
+          <t>videoscope, IPLEX, iplex, IPLEX G, IPLEX UltraLite</t>
         </is>
       </c>
       <c r="I1138" t="inlineStr">
@@ -47110,7 +45646,7 @@
       </c>
       <c r="H1154" t="inlineStr">
         <is>
-          <t>x-ray fluorescence, elemental analysis, remote visual inspection, rvi, videoscope, nondestructive testing, ndt, nde, NDT</t>
+          <t>x-ray fluorescence, elemental analysis, remote visual inspection, rvi, videoscope, nondestructive testing, NDT</t>
         </is>
       </c>
       <c r="I1154" t="inlineStr">
@@ -47362,7 +45898,7 @@
       </c>
       <c r="H1160" t="inlineStr">
         <is>
-          <t>paut, tofd, weld inspection, ndt, NDT</t>
+          <t>paut, tofd, weld inspection, NDT</t>
         </is>
       </c>
       <c r="I1160" t="inlineStr">
@@ -47400,29 +45936,17 @@
       <c r="E1161" t="n">
         <v>275</v>
       </c>
-      <c r="F1161" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G1161" t="inlineStr">
-        <is>
-          <t>Remote Visual Inspection (RVI); Ultrasonic Testing (UT); Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H1161" t="inlineStr">
-        <is>
-          <t>rvi, thickness measurement, nde, inspection system</t>
-        </is>
-      </c>
-      <c r="I1161" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="F1161" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G1161" t="inlineStr"/>
+      <c r="H1161" t="inlineStr"/>
+      <c r="I1161" t="inlineStr"/>
       <c r="J1161" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -47490,17 +46014,17 @@
       </c>
       <c r="G1163" t="inlineStr">
         <is>
-          <t>Ultrasonic Testing (UT); Non-Destructive Testing (NDT/NDE)</t>
+          <t>Ultrasonic Testing (UT)</t>
         </is>
       </c>
       <c r="H1163" t="inlineStr">
         <is>
-          <t>phased array, weld inspection, nde</t>
+          <t>phased array, weld inspection</t>
         </is>
       </c>
       <c r="I1163" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J1163" t="inlineStr">
@@ -47775,12 +46299,12 @@
       </c>
       <c r="G1170" t="inlineStr">
         <is>
-          <t>XRF / XRD Analyzers; Non-Destructive Testing (NDT/NDE)</t>
+          <t>XRF / XRD Analyzers</t>
         </is>
       </c>
       <c r="H1170" t="inlineStr">
         <is>
-          <t>xrf, x-ray fluorescence, positive material identification, pmi, Vanta, Olympus XRF, nde</t>
+          <t>xrf, x-ray fluorescence, positive material identification, pmi, Vanta, Olympus XRF</t>
         </is>
       </c>
       <c r="I1170" t="inlineStr">
@@ -47818,29 +46342,17 @@
       <c r="E1171" t="n">
         <v>5689</v>
       </c>
-      <c r="F1171" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G1171" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H1171" t="inlineStr">
-        <is>
-          <t>ndt, nde</t>
-        </is>
-      </c>
-      <c r="I1171" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="F1171" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G1171" t="inlineStr"/>
+      <c r="H1171" t="inlineStr"/>
+      <c r="I1171" t="inlineStr"/>
       <c r="J1171" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -47868,29 +46380,17 @@
       <c r="E1172" t="n">
         <v>5777</v>
       </c>
-      <c r="F1172" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G1172" t="inlineStr">
-        <is>
-          <t>Industrial Videoscopes / Inspection Tools</t>
-        </is>
-      </c>
-      <c r="H1172" t="inlineStr">
-        <is>
-          <t>3d measurement</t>
-        </is>
-      </c>
-      <c r="I1172" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F1172" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G1172" t="inlineStr"/>
+      <c r="H1172" t="inlineStr"/>
+      <c r="I1172" t="inlineStr"/>
       <c r="J1172" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -48051,7 +46551,7 @@
       </c>
       <c r="H1176" t="inlineStr">
         <is>
-          <t>ultrasonic testing, phased array, EPOCH, OmniScan, nondestructive testing, ndt, nde, NDT</t>
+          <t>ultrasonic testing, phased array, EPOCH, OmniScan, nondestructive testing, NDT</t>
         </is>
       </c>
       <c r="I1176" t="inlineStr">
@@ -48448,7 +46948,7 @@
       <c r="I1186" t="inlineStr"/>
       <c r="J1186" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -48521,7 +47021,7 @@
       </c>
       <c r="H1188" t="inlineStr">
         <is>
-          <t>xrf, x-ray fluorescence, handheld xrf, Vanta, rvi, phased array, OmniScan, nondestructive testing, ndt, nde, inspection system, NDT</t>
+          <t>xrf, x-ray fluorescence, handheld xrf, Vanta, rvi, phased array, OmniScan, nondestructive testing, NDT</t>
         </is>
       </c>
       <c r="I1188" t="inlineStr">
@@ -48642,26 +47142,14 @@
       <c r="E1191" t="n">
         <v>515</v>
       </c>
-      <c r="F1191" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G1191" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H1191" t="inlineStr">
-        <is>
-          <t>inspection system</t>
-        </is>
-      </c>
-      <c r="I1191" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F1191" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G1191" t="inlineStr"/>
+      <c r="H1191" t="inlineStr"/>
+      <c r="I1191" t="inlineStr"/>
       <c r="J1191" t="inlineStr">
         <is>
           <t>Live</t>
@@ -48732,7 +47220,7 @@
       </c>
       <c r="H1193" t="inlineStr">
         <is>
-          <t>xrf, x-ray fluorescence, portable xrf, pxrf, Vanta, remote visual inspection, rvi, videoscope, borescope, IPLEX, ultrasonic testing, ultrasonic inspection, phased array, paut, weld inspection, OmniScan, Omniscan, nondestructive testing, ndt, nde, eddy current, NDT, iplex, IPLEX One</t>
+          <t>xrf, x-ray fluorescence, portable xrf, pxrf, Vanta, remote visual inspection, rvi, videoscope, borescope, IPLEX, ultrasonic testing, ultrasonic inspection, phased array, paut, weld inspection, OmniScan, Omniscan, nondestructive testing, eddy current, NDT, iplex, IPLEX One</t>
         </is>
       </c>
       <c r="I1193" t="inlineStr">
@@ -48975,7 +47463,7 @@
       </c>
       <c r="H1200" t="inlineStr">
         <is>
-          <t>ndt, NDT</t>
+          <t>NDT</t>
         </is>
       </c>
       <c r="I1200" t="inlineStr">
@@ -49020,7 +47508,7 @@
       </c>
       <c r="H1201" t="inlineStr">
         <is>
-          <t>ndt, inspection system, NDT</t>
+          <t>NDT</t>
         </is>
       </c>
       <c r="I1201" t="inlineStr">
@@ -49058,26 +47546,14 @@
       <c r="E1202" t="n">
         <v>3763</v>
       </c>
-      <c r="F1202" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G1202" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H1202" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I1202" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F1202" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G1202" t="inlineStr"/>
+      <c r="H1202" t="inlineStr"/>
+      <c r="I1202" t="inlineStr"/>
       <c r="J1202" t="inlineStr">
         <is>
           <t>Live</t>
@@ -49108,26 +47584,14 @@
       <c r="E1203" t="n">
         <v>3625</v>
       </c>
-      <c r="F1203" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G1203" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H1203" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I1203" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F1203" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G1203" t="inlineStr"/>
+      <c r="H1203" t="inlineStr"/>
+      <c r="I1203" t="inlineStr"/>
       <c r="J1203" t="inlineStr">
         <is>
           <t>Live</t>
@@ -49170,7 +47634,7 @@
       </c>
       <c r="H1204" t="inlineStr">
         <is>
-          <t>ndt, NDT</t>
+          <t>NDT</t>
         </is>
       </c>
       <c r="I1204" t="inlineStr">
@@ -49443,7 +47907,7 @@
       </c>
       <c r="H1211" t="inlineStr">
         <is>
-          <t>rvi, paut, ndt, NDT</t>
+          <t>rvi, paut, NDT</t>
         </is>
       </c>
       <c r="I1211" t="inlineStr">
@@ -49602,12 +48066,12 @@
       </c>
       <c r="H1215" t="inlineStr">
         <is>
-          <t>videoscope, nondestructive testing, nde, inspection system</t>
+          <t>videoscope, nondestructive testing</t>
         </is>
       </c>
       <c r="I1215" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J1215" t="inlineStr">
@@ -49716,26 +48180,14 @@
       <c r="E1218" t="n">
         <v>4927</v>
       </c>
-      <c r="F1218" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G1218" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H1218" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I1218" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F1218" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G1218" t="inlineStr"/>
+      <c r="H1218" t="inlineStr"/>
+      <c r="I1218" t="inlineStr"/>
       <c r="J1218" t="inlineStr">
         <is>
           <t>Live</t>
@@ -49892,7 +48344,7 @@
       </c>
       <c r="H1222" t="inlineStr">
         <is>
-          <t>x-ray fluorescence, rvi, videoscope, fiberscope, non-destructive testing, nde</t>
+          <t>x-ray fluorescence, rvi, videoscope, fiberscope, non-destructive testing</t>
         </is>
       </c>
       <c r="I1222" t="inlineStr">
@@ -49930,26 +48382,14 @@
       <c r="E1223" t="n">
         <v>6004</v>
       </c>
-      <c r="F1223" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G1223" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H1223" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I1223" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F1223" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G1223" t="inlineStr"/>
+      <c r="H1223" t="inlineStr"/>
+      <c r="I1223" t="inlineStr"/>
       <c r="J1223" t="inlineStr">
         <is>
           <t>Live</t>
@@ -50106,7 +48546,7 @@
       </c>
       <c r="H1227" t="inlineStr">
         <is>
-          <t>ndt, NDT</t>
+          <t>NDT</t>
         </is>
       </c>
       <c r="I1227" t="inlineStr">
@@ -50310,26 +48750,14 @@
       <c r="E1232" t="n">
         <v>3916</v>
       </c>
-      <c r="F1232" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G1232" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H1232" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I1232" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F1232" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G1232" t="inlineStr"/>
+      <c r="H1232" t="inlineStr"/>
+      <c r="I1232" t="inlineStr"/>
       <c r="J1232" t="inlineStr">
         <is>
           <t>Live</t>
@@ -50355,26 +48783,14 @@
       <c r="E1233" t="n">
         <v>4908</v>
       </c>
-      <c r="F1233" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G1233" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H1233" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I1233" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F1233" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G1233" t="inlineStr"/>
+      <c r="H1233" t="inlineStr"/>
+      <c r="I1233" t="inlineStr"/>
       <c r="J1233" t="inlineStr">
         <is>
           <t>Live</t>
@@ -50400,26 +48816,14 @@
       <c r="E1234" t="n">
         <v>2748</v>
       </c>
-      <c r="F1234" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G1234" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H1234" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I1234" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F1234" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G1234" t="inlineStr"/>
+      <c r="H1234" t="inlineStr"/>
+      <c r="I1234" t="inlineStr"/>
       <c r="J1234" t="inlineStr">
         <is>
           <t>Live</t>
@@ -50445,26 +48849,14 @@
       <c r="E1235" t="n">
         <v>4144</v>
       </c>
-      <c r="F1235" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G1235" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H1235" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I1235" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F1235" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G1235" t="inlineStr"/>
+      <c r="H1235" t="inlineStr"/>
+      <c r="I1235" t="inlineStr"/>
       <c r="J1235" t="inlineStr">
         <is>
           <t>Live</t>
@@ -50490,26 +48882,14 @@
       <c r="E1236" t="n">
         <v>6372</v>
       </c>
-      <c r="F1236" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G1236" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H1236" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I1236" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F1236" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G1236" t="inlineStr"/>
+      <c r="H1236" t="inlineStr"/>
+      <c r="I1236" t="inlineStr"/>
       <c r="J1236" t="inlineStr">
         <is>
           <t>Live</t>
@@ -50535,26 +48915,14 @@
       <c r="E1237" t="n">
         <v>6260</v>
       </c>
-      <c r="F1237" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G1237" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H1237" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I1237" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F1237" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G1237" t="inlineStr"/>
+      <c r="H1237" t="inlineStr"/>
+      <c r="I1237" t="inlineStr"/>
       <c r="J1237" t="inlineStr">
         <is>
           <t>Live</t>
@@ -50580,26 +48948,14 @@
       <c r="E1238" t="n">
         <v>6483</v>
       </c>
-      <c r="F1238" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G1238" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H1238" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I1238" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F1238" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G1238" t="inlineStr"/>
+      <c r="H1238" t="inlineStr"/>
+      <c r="I1238" t="inlineStr"/>
       <c r="J1238" t="inlineStr">
         <is>
           <t>Live</t>
@@ -50625,26 +48981,14 @@
       <c r="E1239" t="n">
         <v>6322</v>
       </c>
-      <c r="F1239" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G1239" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H1239" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I1239" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F1239" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G1239" t="inlineStr"/>
+      <c r="H1239" t="inlineStr"/>
+      <c r="I1239" t="inlineStr"/>
       <c r="J1239" t="inlineStr">
         <is>
           <t>Live</t>
@@ -50670,26 +49014,14 @@
       <c r="E1240" t="n">
         <v>6471</v>
       </c>
-      <c r="F1240" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G1240" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H1240" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I1240" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F1240" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G1240" t="inlineStr"/>
+      <c r="H1240" t="inlineStr"/>
+      <c r="I1240" t="inlineStr"/>
       <c r="J1240" t="inlineStr">
         <is>
           <t>Live</t>
@@ -50715,26 +49047,14 @@
       <c r="E1241" t="n">
         <v>6502</v>
       </c>
-      <c r="F1241" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G1241" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H1241" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I1241" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F1241" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G1241" t="inlineStr"/>
+      <c r="H1241" t="inlineStr"/>
+      <c r="I1241" t="inlineStr"/>
       <c r="J1241" t="inlineStr">
         <is>
           <t>Live</t>
@@ -50760,26 +49080,14 @@
       <c r="E1242" t="n">
         <v>6200</v>
       </c>
-      <c r="F1242" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G1242" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H1242" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I1242" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F1242" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G1242" t="inlineStr"/>
+      <c r="H1242" t="inlineStr"/>
+      <c r="I1242" t="inlineStr"/>
       <c r="J1242" t="inlineStr">
         <is>
           <t>Live</t>
@@ -50805,26 +49113,14 @@
       <c r="E1243" t="n">
         <v>6549</v>
       </c>
-      <c r="F1243" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G1243" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H1243" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I1243" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F1243" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G1243" t="inlineStr"/>
+      <c r="H1243" t="inlineStr"/>
+      <c r="I1243" t="inlineStr"/>
       <c r="J1243" t="inlineStr">
         <is>
           <t>Live</t>
@@ -50850,26 +49146,14 @@
       <c r="E1244" t="n">
         <v>6453</v>
       </c>
-      <c r="F1244" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G1244" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H1244" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I1244" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F1244" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G1244" t="inlineStr"/>
+      <c r="H1244" t="inlineStr"/>
+      <c r="I1244" t="inlineStr"/>
       <c r="J1244" t="inlineStr">
         <is>
           <t>Live</t>
@@ -50895,26 +49179,14 @@
       <c r="E1245" t="n">
         <v>6482</v>
       </c>
-      <c r="F1245" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G1245" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H1245" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I1245" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F1245" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G1245" t="inlineStr"/>
+      <c r="H1245" t="inlineStr"/>
+      <c r="I1245" t="inlineStr"/>
       <c r="J1245" t="inlineStr">
         <is>
           <t>Live</t>
@@ -50940,26 +49212,14 @@
       <c r="E1246" t="n">
         <v>6340</v>
       </c>
-      <c r="F1246" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G1246" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H1246" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I1246" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F1246" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G1246" t="inlineStr"/>
+      <c r="H1246" t="inlineStr"/>
+      <c r="I1246" t="inlineStr"/>
       <c r="J1246" t="inlineStr">
         <is>
           <t>Live</t>
@@ -51018,26 +49278,14 @@
       <c r="E1248" t="n">
         <v>6369</v>
       </c>
-      <c r="F1248" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G1248" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H1248" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I1248" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F1248" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G1248" t="inlineStr"/>
+      <c r="H1248" t="inlineStr"/>
+      <c r="I1248" t="inlineStr"/>
       <c r="J1248" t="inlineStr">
         <is>
           <t>Live</t>
@@ -51063,26 +49311,14 @@
       <c r="E1249" t="n">
         <v>6148</v>
       </c>
-      <c r="F1249" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G1249" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H1249" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I1249" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F1249" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G1249" t="inlineStr"/>
+      <c r="H1249" t="inlineStr"/>
+      <c r="I1249" t="inlineStr"/>
       <c r="J1249" t="inlineStr">
         <is>
           <t>Live</t>
@@ -51108,26 +49344,14 @@
       <c r="E1250" t="n">
         <v>47</v>
       </c>
-      <c r="F1250" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G1250" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H1250" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I1250" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F1250" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G1250" t="inlineStr"/>
+      <c r="H1250" t="inlineStr"/>
+      <c r="I1250" t="inlineStr"/>
       <c r="J1250" t="inlineStr">
         <is>
           <t>Live</t>
@@ -51153,26 +49377,14 @@
       <c r="E1251" t="n">
         <v>5256</v>
       </c>
-      <c r="F1251" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G1251" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H1251" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I1251" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F1251" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G1251" t="inlineStr"/>
+      <c r="H1251" t="inlineStr"/>
+      <c r="I1251" t="inlineStr"/>
       <c r="J1251" t="inlineStr">
         <is>
           <t>Live</t>
@@ -51198,26 +49410,14 @@
       <c r="E1252" t="n">
         <v>5265</v>
       </c>
-      <c r="F1252" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G1252" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H1252" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I1252" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F1252" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G1252" t="inlineStr"/>
+      <c r="H1252" t="inlineStr"/>
+      <c r="I1252" t="inlineStr"/>
       <c r="J1252" t="inlineStr">
         <is>
           <t>Live</t>
@@ -51253,7 +49453,7 @@
       <c r="I1253" t="inlineStr"/>
       <c r="J1253" t="inlineStr">
         <is>
-          <t>Slug-only</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -51276,26 +49476,14 @@
       <c r="E1254" t="n">
         <v>4446</v>
       </c>
-      <c r="F1254" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G1254" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H1254" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I1254" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F1254" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G1254" t="inlineStr"/>
+      <c r="H1254" t="inlineStr"/>
+      <c r="I1254" t="inlineStr"/>
       <c r="J1254" t="inlineStr">
         <is>
           <t>Live</t>
@@ -51321,26 +49509,14 @@
       <c r="E1255" t="n">
         <v>234</v>
       </c>
-      <c r="F1255" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G1255" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H1255" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I1255" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F1255" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G1255" t="inlineStr"/>
+      <c r="H1255" t="inlineStr"/>
+      <c r="I1255" t="inlineStr"/>
       <c r="J1255" t="inlineStr">
         <is>
           <t>Live</t>
@@ -51366,26 +49542,14 @@
       <c r="E1256" t="n">
         <v>2373</v>
       </c>
-      <c r="F1256" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G1256" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H1256" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I1256" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F1256" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G1256" t="inlineStr"/>
+      <c r="H1256" t="inlineStr"/>
+      <c r="I1256" t="inlineStr"/>
       <c r="J1256" t="inlineStr">
         <is>
           <t>Live</t>
@@ -51411,26 +49575,14 @@
       <c r="E1257" t="n">
         <v>4149</v>
       </c>
-      <c r="F1257" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G1257" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H1257" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I1257" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F1257" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G1257" t="inlineStr"/>
+      <c r="H1257" t="inlineStr"/>
+      <c r="I1257" t="inlineStr"/>
       <c r="J1257" t="inlineStr">
         <is>
           <t>Live</t>
@@ -51456,26 +49608,14 @@
       <c r="E1258" t="n">
         <v>5754</v>
       </c>
-      <c r="F1258" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G1258" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H1258" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I1258" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F1258" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G1258" t="inlineStr"/>
+      <c r="H1258" t="inlineStr"/>
+      <c r="I1258" t="inlineStr"/>
       <c r="J1258" t="inlineStr">
         <is>
           <t>Live</t>
@@ -51501,26 +49641,14 @@
       <c r="E1259" t="n">
         <v>2294</v>
       </c>
-      <c r="F1259" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G1259" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H1259" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I1259" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F1259" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G1259" t="inlineStr"/>
+      <c r="H1259" t="inlineStr"/>
+      <c r="I1259" t="inlineStr"/>
       <c r="J1259" t="inlineStr">
         <is>
           <t>Live</t>
@@ -51836,7 +49964,7 @@
       </c>
       <c r="H1267" t="inlineStr">
         <is>
-          <t>ultrasonic flaw, wall thickness, EPOCH, ndt, nde, NDT</t>
+          <t>ultrasonic flaw, wall thickness, EPOCH, NDT</t>
         </is>
       </c>
       <c r="I1267" t="inlineStr">
@@ -52083,7 +50211,7 @@
       </c>
       <c r="H1273" t="inlineStr">
         <is>
-          <t>videoscope, phased array, weld inspection, OmniScan, ndt, NDT</t>
+          <t>videoscope, phased array, weld inspection, OmniScan, NDT</t>
         </is>
       </c>
       <c r="I1273" t="inlineStr">
@@ -52380,7 +50508,7 @@
       </c>
       <c r="H1280" t="inlineStr">
         <is>
-          <t>xrf, xrd, rvi, nondestructive testing, nde</t>
+          <t>xrf, xrd, rvi, nondestructive testing</t>
         </is>
       </c>
       <c r="I1280" t="inlineStr">
@@ -52594,7 +50722,7 @@
       </c>
       <c r="H1285" t="inlineStr">
         <is>
-          <t>remote visual inspection, rvi, nondestructive testing, nde</t>
+          <t>remote visual inspection, rvi, nondestructive testing</t>
         </is>
       </c>
       <c r="I1285" t="inlineStr">
@@ -52832,12 +50960,12 @@
       </c>
       <c r="H1290" t="inlineStr">
         <is>
-          <t>nondestructive testing, nde</t>
+          <t>nondestructive testing</t>
         </is>
       </c>
       <c r="I1290" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J1290" t="inlineStr">
@@ -52882,7 +51010,7 @@
       </c>
       <c r="H1291" t="inlineStr">
         <is>
-          <t>rvi, phased array, nondestructive testing, nde</t>
+          <t>rvi, phased array, nondestructive testing</t>
         </is>
       </c>
       <c r="I1291" t="inlineStr">
@@ -53365,17 +51493,17 @@
       </c>
       <c r="G1304" t="inlineStr">
         <is>
-          <t>Remote Visual Inspection (RVI); Non-Destructive Testing (NDT/NDE)</t>
+          <t>Remote Visual Inspection (RVI)</t>
         </is>
       </c>
       <c r="H1304" t="inlineStr">
         <is>
-          <t>rvi, nde</t>
+          <t>rvi</t>
         </is>
       </c>
       <c r="I1304" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J1304" t="inlineStr">
@@ -53647,17 +51775,17 @@
       </c>
       <c r="G1311" t="inlineStr">
         <is>
-          <t>Remote Visual Inspection (RVI); Non-Destructive Testing (NDT/NDE)</t>
+          <t>Remote Visual Inspection (RVI)</t>
         </is>
       </c>
       <c r="H1311" t="inlineStr">
         <is>
-          <t>rvi, nde</t>
+          <t>rvi</t>
         </is>
       </c>
       <c r="I1311" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J1311" t="inlineStr">
@@ -54034,7 +52162,7 @@
       </c>
       <c r="H1321" t="inlineStr">
         <is>
-          <t>rvi, ndt, NDT</t>
+          <t>rvi, NDT</t>
         </is>
       </c>
       <c r="I1321" t="inlineStr">
@@ -54143,26 +52271,14 @@
       <c r="E1324" t="n">
         <v>2923</v>
       </c>
-      <c r="F1324" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G1324" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H1324" t="inlineStr">
-        <is>
-          <t>inspection system</t>
-        </is>
-      </c>
-      <c r="I1324" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F1324" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G1324" t="inlineStr"/>
+      <c r="H1324" t="inlineStr"/>
+      <c r="I1324" t="inlineStr"/>
       <c r="J1324" t="inlineStr">
         <is>
           <t>Live</t>
@@ -54276,17 +52392,17 @@
       </c>
       <c r="G1327" t="inlineStr">
         <is>
-          <t>Remote Visual Inspection (RVI); Non-Destructive Testing (NDT/NDE)</t>
+          <t>Remote Visual Inspection (RVI)</t>
         </is>
       </c>
       <c r="H1327" t="inlineStr">
         <is>
-          <t>rvi, nde</t>
+          <t>rvi</t>
         </is>
       </c>
       <c r="I1327" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J1327" t="inlineStr">
@@ -54395,26 +52511,14 @@
       <c r="E1330" t="n">
         <v>613</v>
       </c>
-      <c r="F1330" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G1330" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H1330" t="inlineStr">
-        <is>
-          <t>inspection system</t>
-        </is>
-      </c>
-      <c r="I1330" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F1330" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G1330" t="inlineStr"/>
+      <c r="H1330" t="inlineStr"/>
+      <c r="I1330" t="inlineStr"/>
       <c r="J1330" t="inlineStr">
         <is>
           <t>Live</t>
@@ -54445,26 +52549,14 @@
       <c r="E1331" t="n">
         <v>4832</v>
       </c>
-      <c r="F1331" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G1331" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H1331" t="inlineStr">
-        <is>
-          <t>inspection system</t>
-        </is>
-      </c>
-      <c r="I1331" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F1331" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G1331" t="inlineStr"/>
+      <c r="H1331" t="inlineStr"/>
+      <c r="I1331" t="inlineStr"/>
       <c r="J1331" t="inlineStr">
         <is>
           <t>Live</t>
@@ -54495,26 +52587,14 @@
       <c r="E1332" t="n">
         <v>514</v>
       </c>
-      <c r="F1332" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G1332" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H1332" t="inlineStr">
-        <is>
-          <t>inspection system</t>
-        </is>
-      </c>
-      <c r="I1332" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F1332" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G1332" t="inlineStr"/>
+      <c r="H1332" t="inlineStr"/>
+      <c r="I1332" t="inlineStr"/>
       <c r="J1332" t="inlineStr">
         <is>
           <t>Live</t>
@@ -54545,26 +52625,14 @@
       <c r="E1333" t="n">
         <v>5421</v>
       </c>
-      <c r="F1333" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G1333" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H1333" t="inlineStr">
-        <is>
-          <t>inspection system</t>
-        </is>
-      </c>
-      <c r="I1333" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F1333" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G1333" t="inlineStr"/>
+      <c r="H1333" t="inlineStr"/>
+      <c r="I1333" t="inlineStr"/>
       <c r="J1333" t="inlineStr">
         <is>
           <t>Live</t>
@@ -54605,7 +52673,7 @@
       <c r="I1334" t="inlineStr"/>
       <c r="J1334" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -54747,26 +52815,14 @@
       <c r="E1338" t="n">
         <v>604</v>
       </c>
-      <c r="F1338" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G1338" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H1338" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I1338" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F1338" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G1338" t="inlineStr"/>
+      <c r="H1338" t="inlineStr"/>
+      <c r="I1338" t="inlineStr"/>
       <c r="J1338" t="inlineStr">
         <is>
           <t>Live</t>
@@ -54807,7 +52863,7 @@
       <c r="I1339" t="inlineStr"/>
       <c r="J1339" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -55101,7 +53157,7 @@
       <c r="I1347" t="inlineStr"/>
       <c r="J1347" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -55585,26 +53641,14 @@
       <c r="E1360" t="n">
         <v>5901</v>
       </c>
-      <c r="F1360" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G1360" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H1360" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I1360" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F1360" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G1360" t="inlineStr"/>
+      <c r="H1360" t="inlineStr"/>
+      <c r="I1360" t="inlineStr"/>
       <c r="J1360" t="inlineStr">
         <is>
           <t>Live</t>
@@ -55673,26 +53717,14 @@
       <c r="E1362" t="n">
         <v>767</v>
       </c>
-      <c r="F1362" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G1362" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H1362" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I1362" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F1362" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G1362" t="inlineStr"/>
+      <c r="H1362" t="inlineStr"/>
+      <c r="I1362" t="inlineStr"/>
       <c r="J1362" t="inlineStr">
         <is>
           <t>Live</t>
@@ -55761,26 +53793,14 @@
       <c r="E1364" t="n">
         <v>1918</v>
       </c>
-      <c r="F1364" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G1364" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H1364" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I1364" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F1364" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G1364" t="inlineStr"/>
+      <c r="H1364" t="inlineStr"/>
+      <c r="I1364" t="inlineStr"/>
       <c r="J1364" t="inlineStr">
         <is>
           <t>Live</t>
@@ -55811,26 +53831,14 @@
       <c r="E1365" t="n">
         <v>2564</v>
       </c>
-      <c r="F1365" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G1365" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H1365" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I1365" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F1365" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G1365" t="inlineStr"/>
+      <c r="H1365" t="inlineStr"/>
+      <c r="I1365" t="inlineStr"/>
       <c r="J1365" t="inlineStr">
         <is>
           <t>Live</t>
@@ -55861,26 +53869,14 @@
       <c r="E1366" t="n">
         <v>4793</v>
       </c>
-      <c r="F1366" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G1366" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H1366" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I1366" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F1366" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G1366" t="inlineStr"/>
+      <c r="H1366" t="inlineStr"/>
+      <c r="I1366" t="inlineStr"/>
       <c r="J1366" t="inlineStr">
         <is>
           <t>Live</t>
@@ -55911,26 +53907,14 @@
       <c r="E1367" t="n">
         <v>4581</v>
       </c>
-      <c r="F1367" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G1367" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H1367" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I1367" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F1367" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G1367" t="inlineStr"/>
+      <c r="H1367" t="inlineStr"/>
+      <c r="I1367" t="inlineStr"/>
       <c r="J1367" t="inlineStr">
         <is>
           <t>Live</t>
@@ -55961,26 +53945,14 @@
       <c r="E1368" t="n">
         <v>2091</v>
       </c>
-      <c r="F1368" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G1368" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H1368" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I1368" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F1368" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G1368" t="inlineStr"/>
+      <c r="H1368" t="inlineStr"/>
+      <c r="I1368" t="inlineStr"/>
       <c r="J1368" t="inlineStr">
         <is>
           <t>Live</t>
@@ -56011,26 +53983,14 @@
       <c r="E1369" t="n">
         <v>3366</v>
       </c>
-      <c r="F1369" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G1369" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H1369" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I1369" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F1369" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G1369" t="inlineStr"/>
+      <c r="H1369" t="inlineStr"/>
+      <c r="I1369" t="inlineStr"/>
       <c r="J1369" t="inlineStr">
         <is>
           <t>Live</t>
@@ -56099,26 +54059,14 @@
       <c r="E1371" t="n">
         <v>5562</v>
       </c>
-      <c r="F1371" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G1371" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H1371" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I1371" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F1371" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G1371" t="inlineStr"/>
+      <c r="H1371" t="inlineStr"/>
+      <c r="I1371" t="inlineStr"/>
       <c r="J1371" t="inlineStr">
         <is>
           <t>Live</t>
@@ -56149,26 +54097,14 @@
       <c r="E1372" t="n">
         <v>4745</v>
       </c>
-      <c r="F1372" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G1372" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H1372" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I1372" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F1372" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G1372" t="inlineStr"/>
+      <c r="H1372" t="inlineStr"/>
+      <c r="I1372" t="inlineStr"/>
       <c r="J1372" t="inlineStr">
         <is>
           <t>Live</t>
@@ -56199,26 +54135,14 @@
       <c r="E1373" t="n">
         <v>5461</v>
       </c>
-      <c r="F1373" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G1373" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H1373" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I1373" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F1373" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G1373" t="inlineStr"/>
+      <c r="H1373" t="inlineStr"/>
+      <c r="I1373" t="inlineStr"/>
       <c r="J1373" t="inlineStr">
         <is>
           <t>Live</t>
@@ -56249,26 +54173,14 @@
       <c r="E1374" t="n">
         <v>2931</v>
       </c>
-      <c r="F1374" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G1374" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H1374" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I1374" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F1374" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G1374" t="inlineStr"/>
+      <c r="H1374" t="inlineStr"/>
+      <c r="I1374" t="inlineStr"/>
       <c r="J1374" t="inlineStr">
         <is>
           <t>Live</t>
@@ -56299,26 +54211,14 @@
       <c r="E1375" t="n">
         <v>5322</v>
       </c>
-      <c r="F1375" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G1375" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H1375" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I1375" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F1375" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G1375" t="inlineStr"/>
+      <c r="H1375" t="inlineStr"/>
+      <c r="I1375" t="inlineStr"/>
       <c r="J1375" t="inlineStr">
         <is>
           <t>Live</t>
@@ -56349,26 +54249,14 @@
       <c r="E1376" t="n">
         <v>3867</v>
       </c>
-      <c r="F1376" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G1376" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H1376" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I1376" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F1376" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G1376" t="inlineStr"/>
+      <c r="H1376" t="inlineStr"/>
+      <c r="I1376" t="inlineStr"/>
       <c r="J1376" t="inlineStr">
         <is>
           <t>Live</t>
@@ -56751,7 +54639,7 @@
       <c r="I1386" t="inlineStr"/>
       <c r="J1386" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -56789,7 +54677,7 @@
       <c r="I1387" t="inlineStr"/>
       <c r="J1387" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -56948,7 +54836,7 @@
       <c r="I1391" t="inlineStr"/>
       <c r="J1391" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -57009,26 +54897,14 @@
       <c r="E1393" t="n">
         <v>2542</v>
       </c>
-      <c r="F1393" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G1393" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H1393" t="inlineStr">
-        <is>
-          <t>inspection system</t>
-        </is>
-      </c>
-      <c r="I1393" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F1393" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G1393" t="inlineStr"/>
+      <c r="H1393" t="inlineStr"/>
+      <c r="I1393" t="inlineStr"/>
       <c r="J1393" t="inlineStr">
         <is>
           <t>Live</t>
@@ -57107,7 +54983,7 @@
       <c r="I1395" t="inlineStr"/>
       <c r="J1395" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
@@ -57223,29 +55099,17 @@
       <c r="E1398" t="n">
         <v>775</v>
       </c>
-      <c r="F1398" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G1398" t="inlineStr">
-        <is>
-          <t>Non-Destructive Testing (NDT/NDE)</t>
-        </is>
-      </c>
-      <c r="H1398" t="inlineStr">
-        <is>
-          <t>nde</t>
-        </is>
-      </c>
-      <c r="I1398" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="F1398" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G1398" t="inlineStr"/>
+      <c r="H1398" t="inlineStr"/>
+      <c r="I1398" t="inlineStr"/>
       <c r="J1398" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Title-only (microscopy)</t>
         </is>
       </c>
     </row>
